--- a/Data/National Accounts/PSA-07IOS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-07IOS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF8F6EE-A2F3-4F7A-B009-BA477B78B5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95BE5EA-5E4B-4854-B5BA-8A62B745D6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="IOS" sheetId="7" r:id="rId1"/>
@@ -703,10 +703,10 @@
     <t>Table 8.2.7 Imports of Services</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -756,10 +756,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1237,7 +1239,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1247,7 +1249,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -2025,28 +2027,28 @@
         <v>103057.82977414681</v>
       </c>
       <c r="CT12" s="14">
-        <v>83558.824107262204</v>
+        <v>82959.365119471608</v>
       </c>
       <c r="CU12" s="14">
-        <v>114708.50501852972</v>
+        <v>111429.77111717431</v>
       </c>
       <c r="CV12" s="14">
-        <v>111910.42775467619</v>
+        <v>111511.51365131173</v>
       </c>
       <c r="CW12" s="14">
-        <v>96667.730559925301</v>
+        <v>100031.54965378514</v>
       </c>
       <c r="CX12" s="14">
-        <v>93806.628259242992</v>
+        <v>95236.026584973923</v>
       </c>
       <c r="CY12" s="14">
-        <v>108873.97568325776</v>
+        <v>112016.15709540019</v>
       </c>
       <c r="CZ12" s="14">
-        <v>101328.69263758874</v>
+        <v>101303.52714654528</v>
       </c>
       <c r="DA12" s="14">
-        <v>93342.637592261934</v>
+        <v>98645.294929158903</v>
       </c>
       <c r="DB12" s="7"/>
       <c r="DC12" s="7"/>
@@ -2416,28 +2418,28 @@
         <v>13716.132462195805</v>
       </c>
       <c r="CT13" s="14">
-        <v>23781.286936972505</v>
+        <v>23757.883869761929</v>
       </c>
       <c r="CU13" s="14">
-        <v>39643.405043315986</v>
+        <v>39651.726137464742</v>
       </c>
       <c r="CV13" s="14">
-        <v>27094.070786086289</v>
+        <v>27100.761391271004</v>
       </c>
       <c r="CW13" s="14">
-        <v>14482.425916699527</v>
+        <v>14548.855831225017</v>
       </c>
       <c r="CX13" s="14">
-        <v>26952.449293754966</v>
+        <v>26953.285792976909</v>
       </c>
       <c r="CY13" s="14">
-        <v>41074.467401620401</v>
+        <v>41030.67683590544</v>
       </c>
       <c r="CZ13" s="14">
-        <v>27410.12709311672</v>
+        <v>27434.463307596641</v>
       </c>
       <c r="DA13" s="14">
-        <v>14974.651088512666</v>
+        <v>15276.158061576607</v>
       </c>
       <c r="DB13" s="7"/>
       <c r="DC13" s="7"/>
@@ -3198,28 +3200,28 @@
         <v>5085.0189101476008</v>
       </c>
       <c r="CT15" s="14">
-        <v>5426.0106915642818</v>
+        <v>6241.9288683310479</v>
       </c>
       <c r="CU15" s="14">
-        <v>5335.2208121952963</v>
+        <v>6131.56645141847</v>
       </c>
       <c r="CV15" s="14">
-        <v>5241.4746228091044</v>
+        <v>5966.4072567130279</v>
       </c>
       <c r="CW15" s="14">
-        <v>5330.8345172984846</v>
+        <v>5718.5839708288486</v>
       </c>
       <c r="CX15" s="14">
-        <v>6160.0194403388341</v>
+        <v>6798.8848108326492</v>
       </c>
       <c r="CY15" s="14">
-        <v>6543.1354553816245</v>
+        <v>6557.0210589158714</v>
       </c>
       <c r="CZ15" s="14">
-        <v>5811.2071508160525</v>
+        <v>6632.7499951934087</v>
       </c>
       <c r="DA15" s="14">
-        <v>5413.6029062287753</v>
+        <v>6390.5852836896293</v>
       </c>
       <c r="DB15" s="7"/>
       <c r="DC15" s="7"/>
@@ -3601,16 +3603,16 @@
         <v>23523.707822508699</v>
       </c>
       <c r="CX16" s="14">
-        <v>39841.116232443332</v>
+        <v>38764.840608324004</v>
       </c>
       <c r="CY16" s="14">
-        <v>38304.536626761488</v>
+        <v>38326.227233174162</v>
       </c>
       <c r="CZ16" s="14">
         <v>32515.06985476278</v>
       </c>
       <c r="DA16" s="14">
-        <v>24987.889096676125</v>
+        <v>23606.641598789109</v>
       </c>
       <c r="DB16" s="7"/>
       <c r="DC16" s="7"/>
@@ -3983,25 +3985,25 @@
         <v>128032.85886967613</v>
       </c>
       <c r="CU17" s="14">
-        <v>124444.08686533649</v>
+        <v>128341.61989433496</v>
       </c>
       <c r="CV17" s="14">
-        <v>95987.763063653561</v>
+        <v>96008.928101063779</v>
       </c>
       <c r="CW17" s="14">
         <v>102239.96910638167</v>
       </c>
       <c r="CX17" s="14">
-        <v>140002.03846938146</v>
+        <v>139779.23326947936</v>
       </c>
       <c r="CY17" s="14">
         <v>118999.57961964457</v>
       </c>
       <c r="CZ17" s="14">
-        <v>108824.4942990889</v>
+        <v>108848.39633464041</v>
       </c>
       <c r="DA17" s="14">
-        <v>95558.314796682811</v>
+        <v>92763.140517371517</v>
       </c>
       <c r="DB17" s="7"/>
       <c r="DC17" s="7"/>
@@ -4380,19 +4382,19 @@
         <v>5644.9908527798743</v>
       </c>
       <c r="CW18" s="14">
-        <v>5951.0926922441467</v>
+        <v>6022.2819597726275</v>
       </c>
       <c r="CX18" s="14">
         <v>7511.4556987056058</v>
       </c>
       <c r="CY18" s="14">
-        <v>6347.4583462983701</v>
+        <v>6106.2201389682923</v>
       </c>
       <c r="CZ18" s="14">
-        <v>6013.6473749795132</v>
+        <v>5461.590722876771</v>
       </c>
       <c r="DA18" s="14">
-        <v>5322.3704470860594</v>
+        <v>5422.0053193931162</v>
       </c>
       <c r="DB18" s="7"/>
       <c r="DC18" s="7"/>
@@ -4762,28 +4764,28 @@
         <v>41431.092190080744</v>
       </c>
       <c r="CT19" s="14">
-        <v>41230.54914589347</v>
+        <v>40676.964805711541</v>
       </c>
       <c r="CU19" s="14">
-        <v>48243.039515274832</v>
+        <v>46416.935808331611</v>
       </c>
       <c r="CV19" s="14">
-        <v>27603.561993802265</v>
+        <v>26981.067267331859</v>
       </c>
       <c r="CW19" s="14">
-        <v>45199.403913734452</v>
+        <v>40940.474809284162</v>
       </c>
       <c r="CX19" s="14">
-        <v>38905.463605131474</v>
+        <v>37662.722897327178</v>
       </c>
       <c r="CY19" s="14">
-        <v>41350.583233256519</v>
+        <v>40559.75881696376</v>
       </c>
       <c r="CZ19" s="14">
-        <v>29227.037528739944</v>
+        <v>28531.284934673455</v>
       </c>
       <c r="DA19" s="14">
-        <v>41394.524744193302</v>
+        <v>41340.553391938534</v>
       </c>
       <c r="DB19" s="7"/>
       <c r="DC19" s="7"/>
@@ -5333,28 +5335,28 @@
         <v>584483.06808785535</v>
       </c>
       <c r="CT21" s="22">
-        <v>551855.85069793765</v>
+        <v>551495.32247952139</v>
       </c>
       <c r="CU21" s="22">
-        <v>550911.40276001021</v>
+        <v>550508.7649140819</v>
       </c>
       <c r="CV21" s="22">
-        <v>583436.24790098972</v>
+        <v>583167.62734765373</v>
       </c>
       <c r="CW21" s="22">
-        <v>627487.24521925359</v>
+        <v>627117.50384424743</v>
       </c>
       <c r="CX21" s="22">
-        <v>630779.3680589929</v>
+        <v>630306.64672261383</v>
       </c>
       <c r="CY21" s="22">
-        <v>583082.24846130994</v>
+        <v>585184.15289406164</v>
       </c>
       <c r="CZ21" s="22">
-        <v>619617.84523812344</v>
+        <v>619214.6515953195</v>
       </c>
       <c r="DA21" s="22">
-        <v>659572.60048416874</v>
+        <v>662022.98891444434</v>
       </c>
       <c r="DB21" s="7"/>
       <c r="DC21" s="7"/>
@@ -5915,7 +5917,7 @@
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
@@ -5925,7 +5927,7 @@
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
@@ -6703,28 +6705,28 @@
         <v>96733.456301186729</v>
       </c>
       <c r="CT37" s="14">
-        <v>78301.120542231598</v>
+        <v>77739.138364335653</v>
       </c>
       <c r="CU37" s="14">
-        <v>98035.827816289981</v>
+        <v>95233.652056464765</v>
       </c>
       <c r="CV37" s="14">
-        <v>98058.654879948532</v>
+        <v>97709.116582460207</v>
       </c>
       <c r="CW37" s="14">
-        <v>88121.825853775139</v>
+        <v>91162.329573917261</v>
       </c>
       <c r="CX37" s="14">
-        <v>85766.363187401817</v>
+        <v>87073.944812921516</v>
       </c>
       <c r="CY37" s="14">
-        <v>91715.698223291532</v>
+        <v>94362.679380637186</v>
       </c>
       <c r="CZ37" s="14">
-        <v>88587.786581052322</v>
+        <v>88565.785358183115</v>
       </c>
       <c r="DA37" s="14">
-        <v>83955.343152748697</v>
+        <v>87548.65529400263</v>
       </c>
       <c r="DB37" s="7"/>
       <c r="DC37" s="7"/>
@@ -7094,28 +7096,28 @@
         <v>12281.384203564368</v>
       </c>
       <c r="CT38" s="14">
-        <v>27081.268437274026</v>
+        <v>27054.617871765739</v>
       </c>
       <c r="CU38" s="14">
-        <v>30628.881918549909</v>
+        <v>30635.310877158205</v>
       </c>
       <c r="CV38" s="14">
-        <v>22841.994489547455</v>
+        <v>22847.635087742077</v>
       </c>
       <c r="CW38" s="14">
-        <v>12319.449616532811</v>
+        <v>12375.958104111794</v>
       </c>
       <c r="CX38" s="14">
-        <v>30365.80962963343</v>
+        <v>30366.752066287409</v>
       </c>
       <c r="CY38" s="14">
-        <v>31062.899487361585</v>
+        <v>31029.782516470688</v>
       </c>
       <c r="CZ38" s="14">
-        <v>22873.332765544841</v>
+        <v>22893.640965144277</v>
       </c>
       <c r="DA38" s="14">
-        <v>12599.826992105573</v>
+        <v>12750.127853970469</v>
       </c>
       <c r="DB38" s="7"/>
       <c r="DC38" s="7"/>
@@ -7506,7 +7508,7 @@
         <v>302731.50125422614</v>
       </c>
       <c r="DA39" s="14">
-        <v>353250.6714314025</v>
+        <v>349829.89624523855</v>
       </c>
       <c r="DB39" s="7"/>
       <c r="DC39" s="7"/>
@@ -7876,28 +7878,28 @@
         <v>4643.5022607331684</v>
       </c>
       <c r="CT40" s="14">
-        <v>5496.2086621182261</v>
+        <v>6322.6826234941427</v>
       </c>
       <c r="CU40" s="14">
-        <v>4424.809458974848</v>
+        <v>5085.2652940911039</v>
       </c>
       <c r="CV40" s="14">
-        <v>4512.0231223371584</v>
+        <v>5136.0675071134165</v>
       </c>
       <c r="CW40" s="14">
-        <v>4624.6900689493359</v>
+        <v>4961.0766217795599</v>
       </c>
       <c r="CX40" s="14">
-        <v>6173.3034895051378</v>
+        <v>6813.5465697731643</v>
       </c>
       <c r="CY40" s="14">
-        <v>5311.7538729685275</v>
+        <v>5323.0262833984352</v>
       </c>
       <c r="CZ40" s="14">
-        <v>4951.5688674515759</v>
+        <v>5651.5828001721266</v>
       </c>
       <c r="DA40" s="14">
-        <v>4645.4919118829557</v>
+        <v>5439.7441426085916</v>
       </c>
       <c r="DB40" s="7"/>
       <c r="DC40" s="7"/>
@@ -8279,16 +8281,16 @@
         <v>19676.520679383415</v>
       </c>
       <c r="CX41" s="14">
-        <v>41592.890038442449</v>
+        <v>40469.291657717411</v>
       </c>
       <c r="CY41" s="14">
-        <v>30015.719166177882</v>
+        <v>30032.716086333079</v>
       </c>
       <c r="CZ41" s="14">
         <v>26970.007366173959</v>
       </c>
       <c r="DA41" s="14">
-        <v>20674.260261846979</v>
+        <v>19374.350065721621</v>
       </c>
       <c r="DB41" s="7"/>
       <c r="DC41" s="7"/>
@@ -8661,25 +8663,25 @@
         <v>137746.7522261554</v>
       </c>
       <c r="CU42" s="14">
-        <v>101164.0348174266</v>
+        <v>104332.44704961518</v>
       </c>
       <c r="CV42" s="14">
-        <v>81549.815581517178</v>
+        <v>81567.797091268949</v>
       </c>
       <c r="CW42" s="14">
         <v>86616.009175245388</v>
       </c>
       <c r="CX42" s="14">
-        <v>149020.92757819933</v>
+        <v>148783.76933449332</v>
       </c>
       <c r="CY42" s="14">
         <v>94690.663801736329</v>
       </c>
       <c r="CZ42" s="14">
-        <v>91515.026072785549</v>
+        <v>91535.126284790007</v>
       </c>
       <c r="DA42" s="14">
-        <v>80076.267572132114</v>
+        <v>76965.896518407186</v>
       </c>
       <c r="DB42" s="7"/>
       <c r="DC42" s="7"/>
@@ -9058,19 +9060,19 @@
         <v>4580.0117797002276</v>
       </c>
       <c r="CW43" s="14">
-        <v>4981.4632133290452</v>
+        <v>5041.0533988153402</v>
       </c>
       <c r="CX43" s="14">
         <v>7887.3249578084187</v>
       </c>
       <c r="CY43" s="14">
-        <v>4960.8895363878937</v>
+        <v>4772.3485435637867</v>
       </c>
       <c r="CZ43" s="14">
-        <v>4829.4752941711167</v>
+        <v>4386.1263919049452</v>
       </c>
       <c r="DA43" s="14">
-        <v>4406.7984848920541</v>
+        <v>4453.1831628546961</v>
       </c>
       <c r="DB43" s="7"/>
       <c r="DC43" s="7"/>
@@ -9440,28 +9442,28 @@
         <v>35902.141499991711</v>
       </c>
       <c r="CT44" s="14">
-        <v>43604.131809634338</v>
+        <v>43018.678425260798</v>
       </c>
       <c r="CU44" s="14">
-        <v>38056.287811670802</v>
+        <v>36615.774756447849</v>
       </c>
       <c r="CV44" s="14">
-        <v>22538.892191230167</v>
+        <v>22030.612081124229</v>
       </c>
       <c r="CW44" s="14">
-        <v>37210.115878277022</v>
+        <v>33703.980138159284</v>
       </c>
       <c r="CX44" s="14">
-        <v>40707.281245772516</v>
+        <v>39406.985841980248</v>
       </c>
       <c r="CY44" s="14">
-        <v>31928.848546095251</v>
+        <v>31318.213555243223</v>
       </c>
       <c r="CZ44" s="14">
-        <v>23621.684988389228</v>
+        <v>23059.368380326148</v>
       </c>
       <c r="DA44" s="14">
-        <v>33707.698098062654</v>
+        <v>33392.966917587393</v>
       </c>
       <c r="DB44" s="7"/>
       <c r="DC44" s="7"/>
@@ -10011,28 +10013,28 @@
         <v>550016.79872774554</v>
       </c>
       <c r="CT46" s="22">
-        <v>518911.80086377606</v>
+        <v>518564.18869737419</v>
       </c>
       <c r="CU46" s="22">
-        <v>443199.38167375408</v>
+        <v>442791.98988461902</v>
       </c>
       <c r="CV46" s="22">
-        <v>536080.77601208549</v>
+        <v>535870.62409721385</v>
       </c>
       <c r="CW46" s="22">
-        <v>569464.89010052278</v>
+        <v>569451.74330644251</v>
       </c>
       <c r="CX46" s="22">
-        <v>576975.55187784368</v>
+        <v>576263.26699206198</v>
       </c>
       <c r="CY46" s="22">
-        <v>458076.13952088286</v>
+        <v>459919.09705424664</v>
       </c>
       <c r="CZ46" s="22">
-        <v>566080.38318979484</v>
+        <v>565793.1388009208</v>
       </c>
       <c r="DA46" s="22">
-        <v>593316.35790507356</v>
+        <v>589754.82020039123</v>
       </c>
       <c r="DB46" s="7"/>
       <c r="DC46" s="7"/>
@@ -10593,7 +10595,7 @@
     </row>
     <row r="53" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:179" x14ac:dyDescent="0.2">
@@ -10629,7 +10631,7 @@
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CP56" s="24"/>
       <c r="CQ56" s="24"/>
@@ -11413,28 +11415,28 @@
         <v>1.5188576582565219</v>
       </c>
       <c r="CP62" s="28">
-        <v>-3.4232105159677673</v>
+        <v>-4.1160616311754978</v>
       </c>
       <c r="CQ62" s="28">
-        <v>12.218643778309229</v>
+        <v>9.0110780301492923</v>
       </c>
       <c r="CR62" s="28">
-        <v>13.725389578458973</v>
+        <v>13.320005891490013</v>
       </c>
       <c r="CS62" s="28">
-        <v>-6.2004985242028994</v>
+        <v>-2.936487336278887</v>
       </c>
       <c r="CT62" s="28">
-        <v>12.264179470532</v>
+        <v>14.798403348220447</v>
       </c>
       <c r="CU62" s="28">
-        <v>-5.0863964571149012</v>
+        <v>0.5262381609034037</v>
       </c>
       <c r="CV62" s="28">
-        <v>-9.4555398718376296</v>
+        <v>-9.1541995714326703</v>
       </c>
       <c r="CW62" s="28">
-        <v>-3.4397134890863157</v>
+        <v>-1.3858175040016363</v>
       </c>
       <c r="CX62" s="29"/>
       <c r="CY62" s="29"/>
@@ -11792,28 +11794,28 @@
         <v>3.7370918586490518</v>
       </c>
       <c r="CP63" s="28">
-        <v>-2.8825588532037045</v>
+        <v>-2.9781317298315173</v>
       </c>
       <c r="CQ63" s="28">
-        <v>4.5096115154325247</v>
+        <v>4.5315479337578353</v>
       </c>
       <c r="CR63" s="28">
-        <v>13.487560096471626</v>
+        <v>13.515584695062842</v>
       </c>
       <c r="CS63" s="28">
-        <v>5.5868041272987767</v>
+        <v>6.0711237028685048</v>
       </c>
       <c r="CT63" s="28">
-        <v>13.334696163361485</v>
+        <v>13.449859174040157</v>
       </c>
       <c r="CU63" s="28">
-        <v>3.6098371387139423</v>
+        <v>3.4776561647282449</v>
       </c>
       <c r="CV63" s="28">
-        <v>1.1665146574900689</v>
+        <v>1.2313377897682329</v>
       </c>
       <c r="CW63" s="28">
-        <v>3.398775692997404</v>
+        <v>4.9990338676024351</v>
       </c>
       <c r="CX63" s="29"/>
       <c r="CY63" s="29"/>
@@ -12550,28 +12552,28 @@
         <v>-1.8754270221714933</v>
       </c>
       <c r="CP65" s="28">
-        <v>8.1301894519866238</v>
+        <v>24.38990437814266</v>
       </c>
       <c r="CQ65" s="28">
-        <v>8.7696142684330738</v>
+        <v>25.004782605732373</v>
       </c>
       <c r="CR65" s="28">
-        <v>8.1075277960519259</v>
+        <v>23.059555709912516</v>
       </c>
       <c r="CS65" s="28">
-        <v>4.8341139235556625</v>
+        <v>12.459443551270041</v>
       </c>
       <c r="CT65" s="28">
-        <v>13.527594958773335</v>
+        <v>8.9228178380462424</v>
       </c>
       <c r="CU65" s="28">
-        <v>22.640387074987899</v>
+        <v>6.9387588125865847</v>
       </c>
       <c r="CV65" s="28">
-        <v>10.869699254627065</v>
+        <v>11.16824094987237</v>
       </c>
       <c r="CW65" s="28">
-        <v>1.552634745305042</v>
+        <v>11.751183794602582</v>
       </c>
       <c r="CX65" s="29"/>
       <c r="CY65" s="29"/>
@@ -12941,16 +12943,16 @@
         <v>-2.2044445809542168</v>
       </c>
       <c r="CT66" s="28">
-        <v>8.4309155947755556</v>
+        <v>5.5017418569031094</v>
       </c>
       <c r="CU66" s="28">
-        <v>17.844894767927883</v>
+        <v>17.911626477935513</v>
       </c>
       <c r="CV66" s="28">
         <v>-2.2540957986083185</v>
       </c>
       <c r="CW66" s="28">
-        <v>6.2242792897062742</v>
+        <v>0.35255401446983115</v>
       </c>
       <c r="CX66" s="29"/>
       <c r="CY66" s="29"/>
@@ -13311,25 +13313,25 @@
         <v>19.685045999303625</v>
       </c>
       <c r="CQ67" s="28">
-        <v>6.6053214883170881</v>
+        <v>9.9441523804376146</v>
       </c>
       <c r="CR67" s="28">
-        <v>-8.3494761074292114</v>
+        <v>-8.3292674193116767</v>
       </c>
       <c r="CS67" s="28">
         <v>-8.2470478628054025</v>
       </c>
       <c r="CT67" s="28">
-        <v>9.3485217040171591</v>
+        <v>9.1744998147388088</v>
       </c>
       <c r="CU67" s="28">
-        <v>-4.375063036609788</v>
+        <v>-7.2790418902159644</v>
       </c>
       <c r="CV67" s="28">
-        <v>13.373299705841418</v>
+        <v>13.373202354744734</v>
       </c>
       <c r="CW67" s="28">
-        <v>-6.5352663621665812</v>
+        <v>-9.2692013425291861</v>
       </c>
       <c r="CX67" s="29"/>
       <c r="CY67" s="29"/>
@@ -13696,19 +13698,19 @@
         <v>-0.3771194174866821</v>
       </c>
       <c r="CS68" s="28">
-        <v>2.9188961905423696</v>
+        <v>4.1500517469317231</v>
       </c>
       <c r="CT68" s="28">
         <v>-11.371707136312608</v>
       </c>
       <c r="CU68" s="28">
-        <v>-22.635582113061986</v>
+        <v>-25.575854024111806</v>
       </c>
       <c r="CV68" s="28">
-        <v>6.5306841377447853</v>
+        <v>-3.2489003912696859</v>
       </c>
       <c r="CW68" s="28">
-        <v>-10.564820238432503</v>
+        <v>-9.9675944166881152</v>
       </c>
       <c r="CX68" s="29"/>
       <c r="CY68" s="29"/>
@@ -14066,28 +14068,28 @@
         <v>-3.9541766456909073</v>
       </c>
       <c r="CP69" s="28">
-        <v>133.05044876226955</v>
+        <v>129.92138350411219</v>
       </c>
       <c r="CQ69" s="28">
-        <v>115.30700828211911</v>
+        <v>107.15717091894166</v>
       </c>
       <c r="CR69" s="28">
-        <v>28.074940046354811</v>
+        <v>25.186690522986439</v>
       </c>
       <c r="CS69" s="28">
-        <v>9.0953714335242637</v>
+        <v>-1.1841767978157236</v>
       </c>
       <c r="CT69" s="28">
-        <v>-5.6392301071099666</v>
+        <v>-7.4101937614606044</v>
       </c>
       <c r="CU69" s="28">
-        <v>-14.286944502814762</v>
+        <v>-12.618620530130968</v>
       </c>
       <c r="CV69" s="28">
-        <v>5.881398695219815</v>
+        <v>5.7455757846116313</v>
       </c>
       <c r="CW69" s="28">
-        <v>-8.4179852831753408</v>
+        <v>0.97722018251640463</v>
       </c>
       <c r="CX69" s="29"/>
       <c r="CY69" s="29"/>
@@ -14621,28 +14623,28 @@
         <v>25.334201988982969</v>
       </c>
       <c r="CP71" s="28">
-        <v>28.098403459456847</v>
+        <v>28.014716588831476</v>
       </c>
       <c r="CQ71" s="28">
-        <v>19.508289627673363</v>
+        <v>19.42094607285641</v>
       </c>
       <c r="CR71" s="28">
-        <v>12.86242383573186</v>
+        <v>12.810460717480865</v>
       </c>
       <c r="CS71" s="28">
-        <v>7.357642929176194</v>
+        <v>7.2943833763861221</v>
       </c>
       <c r="CT71" s="28">
-        <v>14.301473339684605</v>
+        <v>14.290479180994126</v>
       </c>
       <c r="CU71" s="28">
-        <v>5.839567948698658</v>
+        <v>6.2987894453218303</v>
       </c>
       <c r="CV71" s="28">
-        <v>6.20146545013327</v>
+        <v>6.1812457614655045</v>
       </c>
       <c r="CW71" s="28">
-        <v>5.1133079611369538</v>
+        <v>5.5660199015695326</v>
       </c>
       <c r="CX71" s="29"/>
       <c r="CY71" s="29"/>
@@ -15207,7 +15209,7 @@
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="CX78" s="25"/>
       <c r="CY78" s="25"/>
@@ -15231,7 +15233,7 @@
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="CX81" s="25"/>
       <c r="CY81" s="25"/>
@@ -16005,28 +16007,28 @@
         <v>-1.2100013989420688</v>
       </c>
       <c r="CP87" s="28">
-        <v>-4.9696728034235917</v>
+        <v>-5.6517237099019013</v>
       </c>
       <c r="CQ87" s="28">
-        <v>7.5100454753433752</v>
+        <v>4.4370664422775263</v>
       </c>
       <c r="CR87" s="28">
-        <v>9.4349681212123784</v>
+        <v>9.0448780012774392</v>
       </c>
       <c r="CS87" s="28">
-        <v>-8.9024322883684022</v>
+        <v>-5.759255318990526</v>
       </c>
       <c r="CT87" s="28">
-        <v>9.5340176404548913</v>
+        <v>12.007859419327431</v>
       </c>
       <c r="CU87" s="28">
-        <v>-6.4467549606882244</v>
+        <v>-0.91456397714452464</v>
       </c>
       <c r="CV87" s="28">
-        <v>-9.6583706053190497</v>
+        <v>-9.3577053442712383</v>
       </c>
       <c r="CW87" s="28">
-        <v>-4.7280939320754527</v>
+        <v>-3.9639994905840439</v>
       </c>
       <c r="CX87" s="29"/>
       <c r="CY87" s="29"/>
@@ -16384,28 +16386,28 @@
         <v>1.8841163992820924</v>
       </c>
       <c r="CP88" s="28">
-        <v>-5.3698940788554523</v>
+        <v>-5.4630191790607512</v>
       </c>
       <c r="CQ88" s="28">
-        <v>1.6888200628687713</v>
+        <v>1.7101644010933512</v>
       </c>
       <c r="CR88" s="28">
-        <v>8.1125636191823816</v>
+        <v>8.1392609170669772</v>
       </c>
       <c r="CS88" s="28">
-        <v>0.30994399603096667</v>
+        <v>0.77005896876003987</v>
       </c>
       <c r="CT88" s="28">
-        <v>12.128461412238138</v>
+        <v>12.242398729195216</v>
       </c>
       <c r="CU88" s="28">
-        <v>1.417020608084357</v>
+        <v>1.2876371351158866</v>
       </c>
       <c r="CV88" s="28">
-        <v>0.13719588283645123</v>
+        <v>0.20135947210957283</v>
       </c>
       <c r="CW88" s="28">
-        <v>2.2758920593050931</v>
+        <v>3.0233598620082631</v>
       </c>
       <c r="CX88" s="29"/>
       <c r="CY88" s="29"/>
@@ -16784,7 +16786,7 @@
         <v>10.436048634375723</v>
       </c>
       <c r="CW89" s="28">
-        <v>11.818330122848323</v>
+        <v>10.735514434225337</v>
       </c>
       <c r="CX89" s="29"/>
       <c r="CY89" s="29"/>
@@ -17142,28 +17144,28 @@
         <v>-3.6281503965314386</v>
       </c>
       <c r="CP90" s="28">
-        <v>5.3607998757746032</v>
+        <v>21.204077123823438</v>
       </c>
       <c r="CQ90" s="28">
-        <v>5.8338422013658402</v>
+        <v>21.630811377719809</v>
       </c>
       <c r="CR90" s="28">
-        <v>2.9873403448610105</v>
+        <v>17.231210489737776</v>
       </c>
       <c r="CS90" s="28">
-        <v>-0.40512937708491847</v>
+        <v>6.8391128767588611</v>
       </c>
       <c r="CT90" s="28">
-        <v>12.319307162657125</v>
+        <v>7.7635392365741183</v>
       </c>
       <c r="CU90" s="28">
-        <v>20.044804690848068</v>
+        <v>4.6754884073324661</v>
       </c>
       <c r="CV90" s="28">
-        <v>9.7416554214540412</v>
+        <v>10.037159604010753</v>
       </c>
       <c r="CW90" s="28">
-        <v>0.44979971897545568</v>
+        <v>9.6484605524462097</v>
       </c>
       <c r="CX90" s="29"/>
       <c r="CY90" s="29"/>
@@ -17533,16 +17535,16 @@
         <v>-7.0919252815139373</v>
       </c>
       <c r="CT91" s="28">
-        <v>7.2768723678186831</v>
+        <v>4.37887417701441</v>
       </c>
       <c r="CU91" s="28">
-        <v>15.350805013192996</v>
+        <v>15.416124401737122</v>
       </c>
       <c r="CV91" s="28">
         <v>-3.2486115697665952</v>
       </c>
       <c r="CW91" s="28">
-        <v>5.0707114266851647</v>
+        <v>-1.5356912870190627</v>
       </c>
       <c r="CX91" s="29"/>
       <c r="CY91" s="29"/>
@@ -17863,25 +17865,25 @@
         <v>16.619717800964452</v>
       </c>
       <c r="CQ92" s="28">
-        <v>3.7279652787626247</v>
+        <v>6.9766786639334839</v>
       </c>
       <c r="CR92" s="28">
-        <v>-12.690227134638931</v>
+        <v>-12.670975570168693</v>
       </c>
       <c r="CS92" s="28">
         <v>-12.832540330928182</v>
       </c>
       <c r="CT92" s="28">
-        <v>8.1847122852913117</v>
+        <v>8.0125425318319969</v>
       </c>
       <c r="CU92" s="28">
-        <v>-6.3988857575450879</v>
+        <v>-9.2414042999429569</v>
       </c>
       <c r="CV92" s="28">
-        <v>12.219782988113749</v>
+        <v>12.219686627515841</v>
       </c>
       <c r="CW92" s="28">
-        <v>-7.5502688999233101</v>
+        <v>-11.141257544334167</v>
       </c>
       <c r="CX92" s="29"/>
       <c r="CY92" s="29"/>
@@ -18208,19 +18210,19 @@
         <v>-5.0954571078311801</v>
       </c>
       <c r="CS93" s="28">
-        <v>-2.2246312090292406</v>
+        <v>-1.0550045124684999</v>
       </c>
       <c r="CT93" s="28">
         <v>-12.314988676775926</v>
       </c>
       <c r="CU93" s="28">
-        <v>-24.27293604691566</v>
+        <v>-27.150979534206243</v>
       </c>
       <c r="CV93" s="28">
-        <v>5.4467876169352962</v>
+        <v>-4.2332945223990777</v>
       </c>
       <c r="CW93" s="28">
-        <v>-11.536062876051034</v>
+        <v>-11.661654607721374</v>
       </c>
       <c r="CX93" s="29"/>
       <c r="CY93" s="29"/>
@@ -18578,28 +18580,28 @@
         <v>-7.8583015358436512</v>
       </c>
       <c r="CP94" s="28">
-        <v>127.08164868150814</v>
+        <v>124.03272386103188</v>
       </c>
       <c r="CQ94" s="28">
-        <v>109.49571341810955</v>
+        <v>101.56584617290005</v>
       </c>
       <c r="CR94" s="28">
-        <v>22.0090562526333</v>
+        <v>19.257599968985971</v>
       </c>
       <c r="CS94" s="28">
-        <v>3.643165347909985</v>
+        <v>-6.1226469229779354</v>
       </c>
       <c r="CT94" s="28">
-        <v>-6.6435230874652262</v>
+        <v>-8.3956381634442465</v>
       </c>
       <c r="CU94" s="28">
-        <v>-16.100990448407416</v>
+        <v>-14.46797517310965</v>
       </c>
       <c r="CV94" s="28">
-        <v>4.8041083296026983</v>
+        <v>4.6696673492941869</v>
       </c>
       <c r="CW94" s="28">
-        <v>-9.4125419863555209</v>
+        <v>-0.92277891007823598</v>
       </c>
       <c r="CX94" s="29"/>
       <c r="CY94" s="29"/>
@@ -19133,28 +19135,28 @@
         <v>21.368816326273304</v>
       </c>
       <c r="CP96" s="28">
-        <v>23.723487698832102</v>
+        <v>23.640606967420339</v>
       </c>
       <c r="CQ96" s="28">
-        <v>15.627164953285416</v>
+        <v>15.520879702107877</v>
       </c>
       <c r="CR96" s="28">
-        <v>8.4946187202017569</v>
+        <v>8.4520871598519705</v>
       </c>
       <c r="CS96" s="28">
-        <v>3.535908615475563</v>
+        <v>3.5335183622849939</v>
       </c>
       <c r="CT96" s="28">
-        <v>11.189522172634199</v>
+        <v>11.126699365728882</v>
       </c>
       <c r="CU96" s="28">
-        <v>3.3566738723656044</v>
+        <v>3.8679803521492175</v>
       </c>
       <c r="CV96" s="28">
-        <v>5.5960982971404007</v>
+        <v>5.5839065173833262</v>
       </c>
       <c r="CW96" s="28">
-        <v>4.188400061036333</v>
+        <v>3.5653726821629732</v>
       </c>
       <c r="CX96" s="29"/>
       <c r="CY96" s="29"/>
@@ -19706,7 +19708,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -19716,7 +19718,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -20494,19 +20496,19 @@
         <v>106.53793807725498</v>
       </c>
       <c r="CT111" s="28">
-        <v>106.71472327422808</v>
+        <v>106.71505610297687</v>
       </c>
       <c r="CU111" s="28">
-        <v>117.00671843510393</v>
+        <v>117.00671843510395</v>
       </c>
       <c r="CV111" s="28">
         <v>114.1260074306405</v>
       </c>
       <c r="CW111" s="28">
-        <v>109.69782982065171</v>
+        <v>109.72904062601476</v>
       </c>
       <c r="CX111" s="28">
-        <v>109.37461351167821</v>
+        <v>109.37373606948513</v>
       </c>
       <c r="CY111" s="28">
         <v>118.70811408772421</v>
@@ -20515,7 +20517,7 @@
         <v>114.38223771950695</v>
       </c>
       <c r="DA111" s="28">
-        <v>111.18129482531441</v>
+        <v>112.67482589868681</v>
       </c>
       <c r="DB111" s="7"/>
       <c r="DC111" s="7"/>
@@ -20906,7 +20908,7 @@
         <v>119.8344262905398</v>
       </c>
       <c r="DA112" s="28">
-        <v>118.84806908773461</v>
+        <v>119.81180296023084</v>
       </c>
       <c r="DB112" s="7"/>
       <c r="DC112" s="7"/>
@@ -21297,7 +21299,7 @@
         <v>101.90137730000251</v>
       </c>
       <c r="DA113" s="28">
-        <v>107.16996185130903</v>
+        <v>108.21791215555088</v>
       </c>
       <c r="DB113" s="7"/>
       <c r="DC113" s="7"/>
@@ -21688,7 +21690,7 @@
         <v>117.36092754389796</v>
       </c>
       <c r="DA114" s="28">
-        <v>116.53454594078674</v>
+        <v>117.47951955374629</v>
       </c>
       <c r="DB114" s="7"/>
       <c r="DC114" s="7"/>
@@ -22079,7 +22081,7 @@
         <v>120.56010743083256</v>
       </c>
       <c r="DA115" s="28">
-        <v>120.8647312174437</v>
+        <v>121.84481811627602</v>
       </c>
       <c r="DB115" s="7"/>
       <c r="DC115" s="7"/>
@@ -22455,22 +22457,22 @@
         <v>123.01218223445123</v>
       </c>
       <c r="CV116" s="28">
-        <v>117.70445141927294</v>
+        <v>117.70445141927293</v>
       </c>
       <c r="CW116" s="28">
         <v>118.03818956784905</v>
       </c>
       <c r="CX116" s="28">
-        <v>93.947904327675602</v>
+        <v>93.947904327675616</v>
       </c>
       <c r="CY116" s="28">
         <v>125.67192460368253</v>
       </c>
       <c r="CZ116" s="28">
-        <v>118.91434551145343</v>
+        <v>118.9143455114534</v>
       </c>
       <c r="DA116" s="28">
-        <v>119.3341269441718</v>
+        <v>120.52499186465822</v>
       </c>
       <c r="DB116" s="7"/>
       <c r="DC116" s="7"/>
@@ -22861,7 +22863,7 @@
         <v>124.51968399626394</v>
       </c>
       <c r="DA117" s="28">
-        <v>120.77635193288019</v>
+        <v>121.75572216790114</v>
       </c>
       <c r="DB117" s="7"/>
       <c r="DC117" s="7"/>
@@ -23231,13 +23233,13 @@
         <v>115.40005821126383</v>
       </c>
       <c r="CT118" s="28">
-        <v>94.556518923244738</v>
+        <v>94.556518923244766</v>
       </c>
       <c r="CU118" s="28">
         <v>126.76759161065635</v>
       </c>
       <c r="CV118" s="28">
-        <v>122.47080184598758</v>
+        <v>122.47080184598759</v>
       </c>
       <c r="CW118" s="28">
         <v>121.47074215407514</v>
@@ -23249,10 +23251,10 @@
         <v>129.50853261607364</v>
       </c>
       <c r="CZ118" s="28">
-        <v>123.72968966060598</v>
+        <v>123.72968966060603</v>
       </c>
       <c r="DA118" s="28">
-        <v>122.80436541162818</v>
+        <v>123.80018072058554</v>
       </c>
       <c r="DB118" s="7"/>
       <c r="DC118" s="7"/>
@@ -23802,28 +23804,28 @@
         <v>106.26640303347723</v>
       </c>
       <c r="CT120" s="28">
-        <v>106.34868002217779</v>
+        <v>106.35044503649003</v>
       </c>
       <c r="CU120" s="28">
-        <v>124.30328776170194</v>
+        <v>124.32672168652627</v>
       </c>
       <c r="CV120" s="28">
-        <v>108.83364485501279</v>
+        <v>108.82619817612162</v>
       </c>
       <c r="CW120" s="28">
-        <v>110.18892580163961</v>
+        <v>110.12654034615412</v>
       </c>
       <c r="CX120" s="28">
-        <v>109.32514662121082</v>
+        <v>109.37824477562896</v>
       </c>
       <c r="CY120" s="28">
-        <v>127.28937356815291</v>
+        <v>127.23632409311332</v>
       </c>
       <c r="CZ120" s="28">
-        <v>109.45757239398608</v>
+        <v>109.44188063284301</v>
       </c>
       <c r="DA120" s="28">
-        <v>111.16710195097903</v>
+        <v>112.25393438742854</v>
       </c>
       <c r="DB120" s="7"/>
       <c r="DC120" s="7"/>
@@ -24024,7 +24026,7 @@
     </row>
     <row r="127" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
@@ -24034,7 +24036,7 @@
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
@@ -24812,28 +24814,28 @@
         <v>17.632303722895166</v>
       </c>
       <c r="CT136" s="17">
-        <v>15.141422166963443</v>
+        <v>15.042623525161837</v>
       </c>
       <c r="CU136" s="17">
-        <v>20.821588452127102</v>
+        <v>20.241234693977162</v>
       </c>
       <c r="CV136" s="17">
-        <v>19.181260704540183</v>
+        <v>19.121691332299289</v>
       </c>
       <c r="CW136" s="17">
-        <v>15.405529163568596</v>
+        <v>15.951005838712684</v>
       </c>
       <c r="CX136" s="17">
-        <v>14.871543523673056</v>
+        <v>15.109475218160838</v>
       </c>
       <c r="CY136" s="17">
-        <v>18.672147192023804</v>
+        <v>19.142035296311064</v>
       </c>
       <c r="CZ136" s="17">
-        <v>16.353417419514027</v>
+        <v>16.360001638454609</v>
       </c>
       <c r="DA136" s="17">
-        <v>14.151988351811829</v>
+        <v>14.900584508539961</v>
       </c>
       <c r="DB136" s="7"/>
       <c r="DC136" s="7"/>
@@ -25203,28 +25205,28 @@
         <v>2.3467116861174997</v>
       </c>
       <c r="CT137" s="17">
-        <v>4.309329493724869</v>
+        <v>4.3079030594396617</v>
       </c>
       <c r="CU137" s="17">
-        <v>7.1959674177565676</v>
+        <v>7.2027420205840329</v>
       </c>
       <c r="CV137" s="17">
-        <v>4.6438785528944724</v>
+        <v>4.6471649180064931</v>
       </c>
       <c r="CW137" s="17">
-        <v>2.3080032346536616</v>
+        <v>2.3199569047331852</v>
       </c>
       <c r="CX137" s="17">
-        <v>4.2728806074764112</v>
+        <v>4.2762179223597085</v>
       </c>
       <c r="CY137" s="17">
-        <v>7.0443693852816498</v>
+        <v>7.0115837267612058</v>
       </c>
       <c r="CZ137" s="17">
-        <v>4.4237149242502554</v>
+        <v>4.4305255434307957</v>
       </c>
       <c r="DA137" s="17">
-        <v>2.2703567548925334</v>
+        <v>2.3074966152800478</v>
       </c>
       <c r="DB137" s="7"/>
       <c r="DC137" s="7"/>
@@ -25594,28 +25596,28 @@
         <v>47.893105794824351</v>
       </c>
       <c r="CT138" s="17">
-        <v>40.700441612530057</v>
+        <v>40.72704865180166</v>
       </c>
       <c r="CU138" s="17">
-        <v>32.278933660846548</v>
+        <v>32.302542222864801</v>
       </c>
       <c r="CV138" s="17">
-        <v>47.424044602290287</v>
+        <v>47.445889218666608</v>
       </c>
       <c r="CW138" s="17">
-        <v>53.24284807952143</v>
+        <v>53.27423945950602</v>
       </c>
       <c r="CX138" s="17">
-        <v>44.009080055077519</v>
+        <v>44.042086261254504</v>
       </c>
       <c r="CY138" s="17">
-        <v>38.002959733354444</v>
+        <v>37.866458105403346</v>
       </c>
       <c r="CZ138" s="17">
-        <v>49.786747052205527</v>
+        <v>49.81916505112661</v>
       </c>
       <c r="DA138" s="17">
-        <v>57.397564655448996</v>
+        <v>57.185115343698754</v>
       </c>
       <c r="DB138" s="7"/>
       <c r="DC138" s="7"/>
@@ -25985,28 +25987,28 @@
         <v>0.87000277472251042</v>
       </c>
       <c r="CT139" s="17">
-        <v>0.98322971201663478</v>
+        <v>1.13181900442371</v>
       </c>
       <c r="CU139" s="17">
-        <v>0.96843535738530395</v>
+        <v>1.1137999687208295</v>
       </c>
       <c r="CV139" s="17">
-        <v>0.89838001009813728</v>
+        <v>1.0231033028786716</v>
       </c>
       <c r="CW139" s="17">
-        <v>0.84955264954203336</v>
+        <v>0.91188396684413564</v>
       </c>
       <c r="CX139" s="17">
-        <v>0.97657275305217739</v>
+        <v>1.0786630358706517</v>
       </c>
       <c r="CY139" s="17">
-        <v>1.1221633779193658</v>
+        <v>1.1205055752941615</v>
       </c>
       <c r="CZ139" s="17">
-        <v>0.93786955870884658</v>
+        <v>1.0711552089578404</v>
       </c>
       <c r="DA139" s="17">
-        <v>0.82077437756735838</v>
+        <v>0.96531168716189519</v>
       </c>
       <c r="DB139" s="7"/>
       <c r="DC139" s="7"/>
@@ -26376,28 +26378,28 @@
         <v>4.1154253124900313</v>
       </c>
       <c r="CT140" s="17">
-        <v>6.6581369121118161</v>
+        <v>6.6624895260707211</v>
       </c>
       <c r="CU140" s="17">
-        <v>5.9000769874687018</v>
+        <v>5.9043922580701</v>
       </c>
       <c r="CV140" s="17">
-        <v>5.7015470869977936</v>
+        <v>5.7041733520055864</v>
       </c>
       <c r="CW140" s="17">
-        <v>3.7488742602710845</v>
+        <v>3.751084554060081</v>
       </c>
       <c r="CX140" s="17">
-        <v>6.3161730154619189</v>
+        <v>6.1501557709867667</v>
       </c>
       <c r="CY140" s="17">
-        <v>6.5693196333524053</v>
+        <v>6.5494301312893759</v>
       </c>
       <c r="CZ140" s="17">
-        <v>5.2476006145799454</v>
+        <v>5.2510175221132567</v>
       </c>
       <c r="DA140" s="17">
-        <v>3.7884971386521222</v>
+        <v>3.5658341166517831</v>
       </c>
       <c r="DB140" s="7"/>
       <c r="DC140" s="7"/>
@@ -26767,28 +26769,28 @@
         <v>19.064645251982178</v>
       </c>
       <c r="CT141" s="17">
-        <v>23.200417048718734</v>
+        <v>23.215583822912723</v>
       </c>
       <c r="CU141" s="17">
-        <v>22.58876585997027</v>
+        <v>23.313274569636558</v>
       </c>
       <c r="CV141" s="17">
-        <v>16.452142527823003</v>
+        <v>16.46335008987533</v>
       </c>
       <c r="CW141" s="17">
-        <v>16.293553356715236</v>
+        <v>16.303159851167905</v>
       </c>
       <c r="CX141" s="17">
-        <v>22.195088418980742</v>
+        <v>22.176385731656989</v>
       </c>
       <c r="CY141" s="17">
-        <v>20.408712481587528</v>
+        <v>20.3354070733333</v>
       </c>
       <c r="CZ141" s="17">
-        <v>17.563163349058627</v>
+        <v>17.578459433123523</v>
       </c>
       <c r="DA141" s="17">
-        <v>14.487914556568429</v>
+        <v>14.012072400911691</v>
       </c>
       <c r="DB141" s="7"/>
       <c r="DC141" s="7"/>
@@ -27158,28 +27160,28 @@
         <v>0.98930376167995948</v>
       </c>
       <c r="CT142" s="17">
-        <v>1.5357696290140215</v>
+        <v>1.5367736054135979</v>
       </c>
       <c r="CU142" s="17">
-        <v>1.489281641608132</v>
+        <v>1.4903708906635058</v>
       </c>
       <c r="CV142" s="17">
-        <v>0.9675420190446995</v>
+        <v>0.96798769137001994</v>
       </c>
       <c r="CW142" s="17">
-        <v>0.94840058305324504</v>
+        <v>0.96031157205083173</v>
       </c>
       <c r="CX142" s="17">
-        <v>1.1908213995361854</v>
+        <v>1.1917144992461512</v>
       </c>
       <c r="CY142" s="17">
-        <v>1.0886042857673366</v>
+        <v>1.0434698391556969</v>
       </c>
       <c r="CZ142" s="17">
-        <v>0.9705413459595289</v>
+        <v>0.88201897497188575</v>
       </c>
       <c r="DA142" s="17">
-        <v>0.80694232040249958</v>
+        <v>0.81900559499963554</v>
       </c>
       <c r="DB142" s="7"/>
       <c r="DC142" s="7"/>
@@ -27549,28 +27551,28 @@
         <v>7.0885016952883086</v>
       </c>
       <c r="CT143" s="17">
-        <v>7.4712534249204348</v>
+        <v>7.3757588047760807</v>
       </c>
       <c r="CU143" s="17">
-        <v>8.7569506228373744</v>
+        <v>8.4316433754830271</v>
       </c>
       <c r="CV143" s="17">
-        <v>4.7312044963114186</v>
+        <v>4.6266400948979927</v>
       </c>
       <c r="CW143" s="17">
-        <v>7.2032386726747086</v>
+        <v>6.5283578529251578</v>
       </c>
       <c r="CX143" s="17">
-        <v>6.1678402267419896</v>
+        <v>5.9753015604644002</v>
       </c>
       <c r="CY143" s="17">
-        <v>7.0917239107134833</v>
+        <v>6.9311102524518402</v>
       </c>
       <c r="CZ143" s="17">
-        <v>4.7169457357232494</v>
+        <v>4.607656627821485</v>
       </c>
       <c r="DA143" s="17">
-        <v>6.27596184465623</v>
+        <v>6.2445797327562484</v>
       </c>
       <c r="DB143" s="7"/>
       <c r="DC143" s="7"/>
@@ -28702,7 +28704,7 @@
     </row>
     <row r="152" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
@@ -28712,7 +28714,7 @@
     </row>
     <row r="155" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="156" spans="1:179" x14ac:dyDescent="0.2">
@@ -29490,28 +29492,28 @@
         <v>17.587363972326436</v>
       </c>
       <c r="CT161" s="17">
-        <v>15.089485421586527</v>
+        <v>14.991227712737984</v>
       </c>
       <c r="CU161" s="17">
-        <v>22.120028111513854</v>
+        <v>21.507537225612499</v>
       </c>
       <c r="CV161" s="17">
-        <v>18.291768566932884</v>
+        <v>18.233713920607546</v>
       </c>
       <c r="CW161" s="17">
-        <v>15.474496739951737</v>
+        <v>16.008789268884463</v>
       </c>
       <c r="CX161" s="17">
-        <v>14.864817566058697</v>
+        <v>15.110098075038497</v>
       </c>
       <c r="CY161" s="17">
-        <v>20.02193310466248</v>
+        <v>20.517234440801506</v>
       </c>
       <c r="CZ161" s="17">
-        <v>15.649329885248948</v>
+        <v>15.653386243933538</v>
       </c>
       <c r="DA161" s="17">
-        <v>14.150181776410916</v>
+        <v>14.844924076119412</v>
       </c>
       <c r="DB161" s="7"/>
       <c r="DC161" s="7"/>
@@ -29881,28 +29883,28 @@
         <v>2.2329107459940634</v>
       </c>
       <c r="CT162" s="17">
-        <v>5.2188576926165071</v>
+        <v>5.2172167807666296</v>
       </c>
       <c r="CU162" s="17">
-        <v>6.9108584499552181</v>
+        <v>6.9186687151095567</v>
       </c>
       <c r="CV162" s="17">
-        <v>4.2609240084058708</v>
+        <v>4.2636476157344321</v>
       </c>
       <c r="CW162" s="17">
-        <v>2.1633378687065616</v>
+        <v>2.1733111276914374</v>
       </c>
       <c r="CX162" s="17">
-        <v>5.2629283044669499</v>
+        <v>5.2695970410874216</v>
       </c>
       <c r="CY162" s="17">
-        <v>6.7811651398938411</v>
+        <v>6.7467914933766666</v>
       </c>
       <c r="CZ162" s="17">
-        <v>4.0406510179095703</v>
+        <v>4.0462917266304288</v>
       </c>
       <c r="DA162" s="17">
-        <v>2.1236271045339117</v>
+        <v>2.1619370316698956</v>
       </c>
       <c r="DB162" s="7"/>
       <c r="DC162" s="7"/>
@@ -30272,28 +30274,28 @@
         <v>49.964957772918765</v>
       </c>
       <c r="CT163" s="17">
-        <v>34.479022754934668</v>
+        <v>34.502135279973025</v>
       </c>
       <c r="CU163" s="17">
-        <v>31.208815900137015</v>
+        <v>31.237529643015826</v>
       </c>
       <c r="CV163" s="17">
-        <v>51.134795288723325</v>
+        <v>51.154848776754314</v>
       </c>
       <c r="CW163" s="17">
-        <v>55.475731885641764</v>
+        <v>55.477012640388992</v>
       </c>
       <c r="CX163" s="17">
-        <v>37.343289685296376</v>
+        <v>37.389447513413799</v>
       </c>
       <c r="CY163" s="17">
-        <v>36.760191670971608</v>
+        <v>36.612888650501638</v>
       </c>
       <c r="CZ163" s="17">
-        <v>53.478535954270413</v>
+        <v>53.505686176365039</v>
       </c>
       <c r="DA163" s="17">
-        <v>59.538333424462934</v>
+        <v>59.317852819985561</v>
       </c>
       <c r="DB163" s="7"/>
       <c r="DC163" s="7"/>
@@ -30663,28 +30665,28 @@
         <v>0.8442473523488998</v>
       </c>
       <c r="CT164" s="17">
-        <v>1.0591797397880112</v>
+        <v>1.2192671151042325</v>
       </c>
       <c r="CU164" s="17">
-        <v>0.99837897838765899</v>
+        <v>1.1484546717785482</v>
       </c>
       <c r="CV164" s="17">
-        <v>0.84166851792414188</v>
+        <v>0.95845289443999593</v>
       </c>
       <c r="CW164" s="17">
-        <v>0.81211153652211621</v>
+        <v>0.87120228888470119</v>
       </c>
       <c r="CX164" s="17">
-        <v>1.069941953244518</v>
+        <v>1.1823669770481868</v>
       </c>
       <c r="CY164" s="17">
-        <v>1.1595788155489322</v>
+        <v>1.1573831827145447</v>
       </c>
       <c r="CZ164" s="17">
-        <v>0.87471126265674159</v>
+        <v>0.99887793127881752</v>
       </c>
       <c r="DA164" s="17">
-        <v>0.78297047603501302</v>
+        <v>0.92237383337710321</v>
       </c>
       <c r="DB164" s="7"/>
       <c r="DC164" s="7"/>
@@ -31054,28 +31056,28 @@
         <v>3.8505156403456411</v>
       </c>
       <c r="CT165" s="17">
-        <v>7.4717003664664992</v>
+        <v>7.4767089150853643</v>
       </c>
       <c r="CU165" s="17">
-        <v>5.8712284319907813</v>
+        <v>5.8766302692190306</v>
       </c>
       <c r="CV165" s="17">
-        <v>5.1998836405200608</v>
+        <v>5.2019228743482007</v>
       </c>
       <c r="CW165" s="17">
-        <v>3.4552649375644715</v>
+        <v>3.4553447084268156</v>
       </c>
       <c r="CX165" s="17">
-        <v>7.2087785874241739</v>
+        <v>7.0227088859847244</v>
       </c>
       <c r="CY165" s="17">
-        <v>6.5525611522949712</v>
+        <v>6.529999793157268</v>
       </c>
       <c r="CZ165" s="17">
-        <v>4.7643423384857844</v>
+        <v>4.7667611210929852</v>
       </c>
       <c r="DA165" s="17">
-        <v>3.4845255800539912</v>
+        <v>3.2851533217038336</v>
       </c>
       <c r="DB165" s="7"/>
       <c r="DC165" s="7"/>
@@ -31445,28 +31447,28 @@
         <v>18.066242121222395</v>
       </c>
       <c r="CT166" s="17">
-        <v>26.545311167883128</v>
+        <v>26.563105441618184</v>
       </c>
       <c r="CU166" s="17">
-        <v>22.825851975555103</v>
+        <v>23.562406148494627</v>
       </c>
       <c r="CV166" s="17">
-        <v>15.212225326968021</v>
+        <v>15.221546661320904</v>
       </c>
       <c r="CW166" s="17">
-        <v>15.2100701344302</v>
+        <v>15.210421285624934</v>
       </c>
       <c r="CX166" s="17">
-        <v>25.827944891805366</v>
+        <v>25.818714788312686</v>
       </c>
       <c r="CY166" s="17">
-        <v>20.671380941337929</v>
+        <v>20.588547944241537</v>
       </c>
       <c r="CZ166" s="17">
-        <v>16.166436568091157</v>
+        <v>16.178196589442457</v>
       </c>
       <c r="DA166" s="17">
-        <v>13.496386287893946</v>
+        <v>13.050490455042851</v>
       </c>
       <c r="DB166" s="7"/>
       <c r="DC166" s="7"/>
@@ -31836,28 +31838,28 @@
         <v>0.92629967315281059</v>
       </c>
       <c r="CT167" s="17">
-        <v>1.7334480246450339</v>
+        <v>1.7346100170007066</v>
       </c>
       <c r="CU167" s="17">
-        <v>1.478118634046272</v>
+        <v>1.4794785804966017</v>
       </c>
       <c r="CV167" s="17">
-        <v>0.85435105764676311</v>
+        <v>0.85468610775524689</v>
       </c>
       <c r="CW167" s="17">
-        <v>0.87476213194631003</v>
+        <v>0.88524681117756587</v>
       </c>
       <c r="CX167" s="17">
-        <v>1.3670119872736497</v>
+        <v>1.3687016698076413</v>
       </c>
       <c r="CY167" s="17">
-        <v>1.0829836152515289</v>
+        <v>1.0376495723118226</v>
       </c>
       <c r="CZ167" s="17">
-        <v>0.85314302307343792</v>
+        <v>0.77521731726906662</v>
       </c>
       <c r="DA167" s="17">
-        <v>0.74274009576474731</v>
+        <v>0.75509059194150552</v>
       </c>
       <c r="DB167" s="7"/>
       <c r="DC167" s="7"/>
@@ -32227,28 +32229,28 @@
         <v>6.5274627216909824</v>
       </c>
       <c r="CT168" s="17">
-        <v>8.4029948320796084</v>
+        <v>8.2957287377138602</v>
       </c>
       <c r="CU168" s="17">
-        <v>8.5867195184140908</v>
+        <v>8.2692947462733102</v>
       </c>
       <c r="CV168" s="17">
-        <v>4.2043835928789299</v>
+        <v>4.1111811490393606</v>
       </c>
       <c r="CW168" s="17">
-        <v>6.5342247652368233</v>
+        <v>5.9186718689211135</v>
       </c>
       <c r="CX168" s="17">
-        <v>7.0552870244302817</v>
+        <v>6.83836504930707</v>
       </c>
       <c r="CY168" s="17">
-        <v>6.9702055600387087</v>
+        <v>6.8095049228950142</v>
       </c>
       <c r="CZ168" s="17">
-        <v>4.1728499502639318</v>
+        <v>4.0755828939876535</v>
       </c>
       <c r="DA168" s="17">
-        <v>5.6812352548445411</v>
+        <v>5.6621778701598204</v>
       </c>
       <c r="DB168" s="7"/>
       <c r="DC168" s="7"/>

--- a/Data/National Accounts/PSA-07IOS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-07IOS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95BE5EA-5E4B-4854-B5BA-8A62B745D6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1783EFDD-1A71-4534-B669-3BD4849ADB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="IOS" sheetId="7" r:id="rId1"/>
@@ -359,7 +359,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">IOS!$A$1:$DA$173</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">IOS!$A$1:$DB$173</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="59">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -703,10 +703,13 @@
     <t>Table 8.2.7 Imports of Services</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1223,8 +1226,8 @@
   <cols>
     <col min="1" max="1" width="54.85546875" style="1" customWidth="1"/>
     <col min="2" max="93" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="94" max="105" width="15" style="18" bestFit="1" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="1"/>
+    <col min="94" max="106" width="15" style="18" bestFit="1" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1239,7 +1242,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1249,7 +1252,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1415,6 +1418,9 @@
       <c r="CY9" s="19"/>
       <c r="CZ9" s="19"/>
       <c r="DA9" s="19"/>
+      <c r="DB9" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
@@ -1729,6 +1735,9 @@
       </c>
       <c r="DA10" s="20" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="20" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2050,7 +2059,9 @@
       <c r="DA12" s="14">
         <v>98645.294929158903</v>
       </c>
-      <c r="DB12" s="7"/>
+      <c r="DB12" s="14">
+        <v>99602.591382005063</v>
+      </c>
       <c r="DC12" s="7"/>
       <c r="DD12" s="7"/>
       <c r="DE12" s="7"/>
@@ -2441,7 +2452,9 @@
       <c r="DA13" s="14">
         <v>15276.158061576607</v>
       </c>
-      <c r="DB13" s="7"/>
+      <c r="DB13" s="14">
+        <v>29570.037516300414</v>
+      </c>
       <c r="DC13" s="7"/>
       <c r="DD13" s="7"/>
       <c r="DE13" s="7"/>
@@ -2832,7 +2845,9 @@
       <c r="DA14" s="14">
         <v>378578.60981252702</v>
       </c>
-      <c r="DB14" s="7"/>
+      <c r="DB14" s="14">
+        <v>323956.46696176101</v>
+      </c>
       <c r="DC14" s="7"/>
       <c r="DD14" s="7"/>
       <c r="DE14" s="7"/>
@@ -3223,7 +3238,9 @@
       <c r="DA15" s="14">
         <v>6390.5852836896293</v>
       </c>
-      <c r="DB15" s="7"/>
+      <c r="DB15" s="14">
+        <v>6446.225336212291</v>
+      </c>
       <c r="DC15" s="7"/>
       <c r="DD15" s="7"/>
       <c r="DE15" s="7"/>
@@ -3614,7 +3631,9 @@
       <c r="DA16" s="14">
         <v>23606.641598789109</v>
       </c>
-      <c r="DB16" s="7"/>
+      <c r="DB16" s="14">
+        <v>37343.797092214227</v>
+      </c>
       <c r="DC16" s="7"/>
       <c r="DD16" s="7"/>
       <c r="DE16" s="7"/>
@@ -4005,7 +4024,9 @@
       <c r="DA17" s="14">
         <v>92763.140517371517</v>
       </c>
-      <c r="DB17" s="7"/>
+      <c r="DB17" s="14">
+        <v>124042.12099258775</v>
+      </c>
       <c r="DC17" s="7"/>
       <c r="DD17" s="7"/>
       <c r="DE17" s="7"/>
@@ -4396,7 +4417,9 @@
       <c r="DA18" s="14">
         <v>5422.0053193931162</v>
       </c>
-      <c r="DB18" s="7"/>
+      <c r="DB18" s="14">
+        <v>6846.5994558914144</v>
+      </c>
       <c r="DC18" s="7"/>
       <c r="DD18" s="7"/>
       <c r="DE18" s="7"/>
@@ -4787,7 +4810,9 @@
       <c r="DA19" s="14">
         <v>41340.553391938534</v>
       </c>
-      <c r="DB19" s="7"/>
+      <c r="DB19" s="14">
+        <v>45386.14028193547</v>
+      </c>
       <c r="DC19" s="7"/>
       <c r="DD19" s="7"/>
       <c r="DE19" s="7"/>
@@ -4967,7 +4992,7 @@
       <c r="CY20" s="21"/>
       <c r="CZ20" s="21"/>
       <c r="DA20" s="21"/>
-      <c r="DB20" s="7"/>
+      <c r="DB20" s="21"/>
       <c r="DC20" s="7"/>
       <c r="DD20" s="7"/>
       <c r="DE20" s="7"/>
@@ -5358,7 +5383,9 @@
       <c r="DA21" s="22">
         <v>662022.98891444434</v>
       </c>
-      <c r="DB21" s="7"/>
+      <c r="DB21" s="22">
+        <v>673193.97901890764</v>
+      </c>
       <c r="DC21" s="7"/>
       <c r="DD21" s="7"/>
       <c r="DE21" s="7"/>
@@ -5539,6 +5566,7 @@
       <c r="CY22" s="23"/>
       <c r="CZ22" s="23"/>
       <c r="DA22" s="23"/>
+      <c r="DB22" s="23"/>
     </row>
     <row r="23" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
@@ -5650,7 +5678,7 @@
       <c r="CY24" s="21"/>
       <c r="CZ24" s="21"/>
       <c r="DA24" s="21"/>
-      <c r="DB24" s="7"/>
+      <c r="DB24" s="21"/>
       <c r="DC24" s="7"/>
       <c r="DD24" s="7"/>
       <c r="DE24" s="7"/>
@@ -5830,7 +5858,7 @@
       <c r="CY25" s="21"/>
       <c r="CZ25" s="21"/>
       <c r="DA25" s="21"/>
-      <c r="DB25" s="7"/>
+      <c r="DB25" s="21"/>
       <c r="DC25" s="7"/>
       <c r="DD25" s="7"/>
       <c r="DE25" s="7"/>
@@ -5917,7 +5945,7 @@
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
@@ -5927,7 +5955,7 @@
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
@@ -6093,6 +6121,9 @@
       <c r="CY34" s="19"/>
       <c r="CZ34" s="19"/>
       <c r="DA34" s="19"/>
+      <c r="DB34" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="35" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
@@ -6407,6 +6438,9 @@
       </c>
       <c r="DA35" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB35" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -6728,7 +6762,9 @@
       <c r="DA37" s="14">
         <v>87548.65529400263</v>
       </c>
-      <c r="DB37" s="7"/>
+      <c r="DB37" s="14">
+        <v>90042.041266482222</v>
+      </c>
       <c r="DC37" s="7"/>
       <c r="DD37" s="7"/>
       <c r="DE37" s="7"/>
@@ -7119,7 +7155,9 @@
       <c r="DA38" s="14">
         <v>12750.127853970469</v>
       </c>
-      <c r="DB38" s="7"/>
+      <c r="DB38" s="14">
+        <v>32911.238863571496</v>
+      </c>
       <c r="DC38" s="7"/>
       <c r="DD38" s="7"/>
       <c r="DE38" s="7"/>
@@ -7510,7 +7548,9 @@
       <c r="DA39" s="14">
         <v>349829.89624523855</v>
       </c>
-      <c r="DB39" s="7"/>
+      <c r="DB39" s="14">
+        <v>248144.30238961388</v>
+      </c>
       <c r="DC39" s="7"/>
       <c r="DD39" s="7"/>
       <c r="DE39" s="7"/>
@@ -7901,7 +7941,9 @@
       <c r="DA40" s="14">
         <v>5439.7441426085916</v>
       </c>
-      <c r="DB40" s="7"/>
+      <c r="DB40" s="14">
+        <v>6381.8524035509326</v>
+      </c>
       <c r="DC40" s="7"/>
       <c r="DD40" s="7"/>
       <c r="DE40" s="7"/>
@@ -8292,7 +8334,9 @@
       <c r="DA41" s="14">
         <v>19374.350065721621</v>
       </c>
-      <c r="DB41" s="7"/>
+      <c r="DB41" s="14">
+        <v>38513.394891101685</v>
+      </c>
       <c r="DC41" s="7"/>
       <c r="DD41" s="7"/>
       <c r="DE41" s="7"/>
@@ -8683,7 +8727,9 @@
       <c r="DA42" s="14">
         <v>76965.896518407186</v>
       </c>
-      <c r="DB42" s="7"/>
+      <c r="DB42" s="14">
+        <v>130433.09945811037</v>
+      </c>
       <c r="DC42" s="7"/>
       <c r="DD42" s="7"/>
       <c r="DE42" s="7"/>
@@ -9074,7 +9120,9 @@
       <c r="DA43" s="14">
         <v>4453.1831628546961</v>
       </c>
-      <c r="DB43" s="7"/>
+      <c r="DB43" s="14">
+        <v>7102.0916572979395</v>
+      </c>
       <c r="DC43" s="7"/>
       <c r="DD43" s="7"/>
       <c r="DE43" s="7"/>
@@ -9465,7 +9513,9 @@
       <c r="DA44" s="14">
         <v>33392.966917587393</v>
       </c>
-      <c r="DB44" s="7"/>
+      <c r="DB44" s="14">
+        <v>46912.705704721244</v>
+      </c>
       <c r="DC44" s="7"/>
       <c r="DD44" s="7"/>
       <c r="DE44" s="7"/>
@@ -9645,7 +9695,7 @@
       <c r="CY45" s="21"/>
       <c r="CZ45" s="21"/>
       <c r="DA45" s="21"/>
-      <c r="DB45" s="7"/>
+      <c r="DB45" s="21"/>
       <c r="DC45" s="7"/>
       <c r="DD45" s="7"/>
       <c r="DE45" s="7"/>
@@ -10036,7 +10086,9 @@
       <c r="DA46" s="22">
         <v>589754.82020039123</v>
       </c>
-      <c r="DB46" s="7"/>
+      <c r="DB46" s="22">
+        <v>600440.72663444979</v>
+      </c>
       <c r="DC46" s="7"/>
       <c r="DD46" s="7"/>
       <c r="DE46" s="7"/>
@@ -10217,6 +10269,7 @@
       <c r="CY47" s="23"/>
       <c r="CZ47" s="23"/>
       <c r="DA47" s="23"/>
+      <c r="DB47" s="23"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
@@ -10328,7 +10381,7 @@
       <c r="CY49" s="21"/>
       <c r="CZ49" s="21"/>
       <c r="DA49" s="21"/>
-      <c r="DB49" s="7"/>
+      <c r="DB49" s="21"/>
       <c r="DC49" s="7"/>
       <c r="DD49" s="7"/>
       <c r="DE49" s="7"/>
@@ -10508,7 +10561,7 @@
       <c r="CY50" s="21"/>
       <c r="CZ50" s="21"/>
       <c r="DA50" s="21"/>
-      <c r="DB50" s="7"/>
+      <c r="DB50" s="21"/>
       <c r="DC50" s="7"/>
       <c r="DD50" s="7"/>
       <c r="DE50" s="7"/>
@@ -10595,7 +10648,7 @@
     </row>
     <row r="53" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:179" x14ac:dyDescent="0.2">
@@ -10611,6 +10664,7 @@
       <c r="CY54" s="24"/>
       <c r="CZ54" s="24"/>
       <c r="DA54" s="24"/>
+      <c r="DB54" s="24"/>
     </row>
     <row r="55" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
@@ -10628,10 +10682,11 @@
       <c r="CY55" s="24"/>
       <c r="CZ55" s="24"/>
       <c r="DA55" s="24"/>
+      <c r="DB55" s="24"/>
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="CP56" s="24"/>
       <c r="CQ56" s="24"/>
@@ -10645,6 +10700,7 @@
       <c r="CY56" s="24"/>
       <c r="CZ56" s="24"/>
       <c r="DA56" s="24"/>
+      <c r="DB56" s="24"/>
     </row>
     <row r="57" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
@@ -10656,12 +10712,14 @@
       <c r="CY57" s="25"/>
       <c r="CZ57" s="25"/>
       <c r="DA57" s="25"/>
+      <c r="DB57" s="25"/>
     </row>
     <row r="58" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CX58" s="25"/>
       <c r="CY58" s="25"/>
       <c r="CZ58" s="25"/>
       <c r="DA58" s="25"/>
+      <c r="DB58" s="25"/>
     </row>
     <row r="59" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -10815,10 +10873,13 @@
       <c r="CU59" s="19"/>
       <c r="CV59" s="19"/>
       <c r="CW59" s="19"/>
-      <c r="CX59" s="26"/>
+      <c r="CX59" s="19" t="s">
+        <v>58</v>
+      </c>
       <c r="CY59" s="26"/>
       <c r="CZ59" s="26"/>
       <c r="DA59" s="26"/>
+      <c r="DB59" s="26"/>
     </row>
     <row r="60" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
@@ -11122,17 +11183,20 @@
       <c r="CW60" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CX60" s="27"/>
+      <c r="CX60" s="15" t="s">
+        <v>2</v>
+      </c>
       <c r="CY60" s="27"/>
       <c r="CZ60" s="27"/>
       <c r="DA60" s="27"/>
+      <c r="DB60" s="27"/>
     </row>
     <row r="61" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
-      <c r="CX61" s="25"/>
       <c r="CY61" s="25"/>
       <c r="CZ61" s="25"/>
       <c r="DA61" s="25"/>
+      <c r="DB61" s="25"/>
     </row>
     <row r="62" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
@@ -11438,11 +11502,13 @@
       <c r="CW62" s="28">
         <v>-1.3858175040016363</v>
       </c>
-      <c r="CX62" s="29"/>
+      <c r="CX62" s="28">
+        <v>4.5849926268554384</v>
+      </c>
       <c r="CY62" s="29"/>
       <c r="CZ62" s="29"/>
       <c r="DA62" s="29"/>
-      <c r="DB62" s="7"/>
+      <c r="DB62" s="29"/>
       <c r="DC62" s="7"/>
       <c r="DD62" s="7"/>
       <c r="DE62" s="7"/>
@@ -11817,11 +11883,13 @@
       <c r="CW63" s="28">
         <v>4.9990338676024351</v>
       </c>
-      <c r="CX63" s="29"/>
+      <c r="CX63" s="28">
+        <v>9.7084702155510172</v>
+      </c>
       <c r="CY63" s="29"/>
       <c r="CZ63" s="29"/>
       <c r="DA63" s="29"/>
-      <c r="DB63" s="7"/>
+      <c r="DB63" s="29"/>
       <c r="DC63" s="7"/>
       <c r="DD63" s="7"/>
       <c r="DE63" s="7"/>
@@ -12196,11 +12264,13 @@
       <c r="CW64" s="28">
         <v>13.315649095939762</v>
       </c>
-      <c r="CX64" s="29"/>
+      <c r="CX64" s="28">
+        <v>16.69893263503279</v>
+      </c>
       <c r="CY64" s="29"/>
       <c r="CZ64" s="29"/>
       <c r="DA64" s="29"/>
-      <c r="DB64" s="7"/>
+      <c r="DB64" s="29"/>
       <c r="DC64" s="7"/>
       <c r="DD64" s="7"/>
       <c r="DE64" s="7"/>
@@ -12575,11 +12645,13 @@
       <c r="CW65" s="28">
         <v>11.751183794602582</v>
       </c>
-      <c r="CX65" s="29"/>
+      <c r="CX65" s="28">
+        <v>-5.1870194073367202</v>
+      </c>
       <c r="CY65" s="29"/>
       <c r="CZ65" s="29"/>
       <c r="DA65" s="29"/>
-      <c r="DB65" s="7"/>
+      <c r="DB65" s="29"/>
       <c r="DC65" s="7"/>
       <c r="DD65" s="7"/>
       <c r="DE65" s="7"/>
@@ -12954,11 +13026,13 @@
       <c r="CW66" s="28">
         <v>0.35255401446983115</v>
       </c>
-      <c r="CX66" s="29"/>
+      <c r="CX66" s="28">
+        <v>-3.665805131169904</v>
+      </c>
       <c r="CY66" s="29"/>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
-      <c r="DB66" s="7"/>
+      <c r="DB66" s="29"/>
       <c r="DC66" s="7"/>
       <c r="DD66" s="7"/>
       <c r="DE66" s="7"/>
@@ -13333,11 +13407,13 @@
       <c r="CW67" s="28">
         <v>-9.2692013425291861</v>
       </c>
-      <c r="CX67" s="29"/>
+      <c r="CX67" s="28">
+        <v>-11.258548146813879</v>
+      </c>
       <c r="CY67" s="29"/>
       <c r="CZ67" s="29"/>
       <c r="DA67" s="29"/>
-      <c r="DB67" s="7"/>
+      <c r="DB67" s="29"/>
       <c r="DC67" s="7"/>
       <c r="DD67" s="7"/>
       <c r="DE67" s="7"/>
@@ -13712,11 +13788,13 @@
       <c r="CW68" s="28">
         <v>-9.9675944166881152</v>
       </c>
-      <c r="CX68" s="29"/>
+      <c r="CX68" s="28">
+        <v>-8.8512303005229853</v>
+      </c>
       <c r="CY68" s="29"/>
       <c r="CZ68" s="29"/>
       <c r="DA68" s="29"/>
-      <c r="DB68" s="7"/>
+      <c r="DB68" s="29"/>
       <c r="DC68" s="7"/>
       <c r="DD68" s="7"/>
       <c r="DE68" s="7"/>
@@ -14091,11 +14169,13 @@
       <c r="CW69" s="28">
         <v>0.97722018251640463</v>
       </c>
-      <c r="CX69" s="29"/>
+      <c r="CX69" s="28">
+        <v>20.506795022928088</v>
+      </c>
       <c r="CY69" s="29"/>
       <c r="CZ69" s="29"/>
       <c r="DA69" s="29"/>
-      <c r="DB69" s="7"/>
+      <c r="DB69" s="29"/>
       <c r="DC69" s="7"/>
       <c r="DD69" s="7"/>
       <c r="DE69" s="7"/>
@@ -14267,11 +14347,11 @@
       <c r="CU70" s="21"/>
       <c r="CV70" s="21"/>
       <c r="CW70" s="21"/>
-      <c r="CX70" s="30"/>
+      <c r="CX70" s="21"/>
       <c r="CY70" s="30"/>
       <c r="CZ70" s="30"/>
       <c r="DA70" s="30"/>
-      <c r="DB70" s="7"/>
+      <c r="DB70" s="30"/>
       <c r="DC70" s="7"/>
       <c r="DD70" s="7"/>
       <c r="DE70" s="7"/>
@@ -14646,11 +14726,13 @@
       <c r="CW71" s="28">
         <v>5.5660199015695326</v>
       </c>
-      <c r="CX71" s="29"/>
+      <c r="CX71" s="28">
+        <v>6.8042011803768503</v>
+      </c>
       <c r="CY71" s="29"/>
       <c r="CZ71" s="29"/>
       <c r="DA71" s="29"/>
-      <c r="DB71" s="7"/>
+      <c r="DB71" s="29"/>
       <c r="DC71" s="7"/>
       <c r="DD71" s="7"/>
       <c r="DE71" s="7"/>
@@ -14823,19 +14905,20 @@
       <c r="CU72" s="23"/>
       <c r="CV72" s="23"/>
       <c r="CW72" s="23"/>
-      <c r="CX72" s="31"/>
+      <c r="CX72" s="23"/>
       <c r="CY72" s="31"/>
       <c r="CZ72" s="31"/>
       <c r="DA72" s="31"/>
+      <c r="DB72" s="31"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CX73" s="25"/>
       <c r="CY73" s="25"/>
       <c r="CZ73" s="25"/>
       <c r="DA73" s="25"/>
+      <c r="DB73" s="25"/>
     </row>
     <row r="74" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="7"/>
@@ -14938,11 +15021,11 @@
       <c r="CU74" s="21"/>
       <c r="CV74" s="21"/>
       <c r="CW74" s="21"/>
-      <c r="CX74" s="30"/>
+      <c r="CX74" s="21"/>
       <c r="CY74" s="30"/>
       <c r="CZ74" s="30"/>
       <c r="DA74" s="30"/>
-      <c r="DB74" s="7"/>
+      <c r="DB74" s="30"/>
       <c r="DC74" s="7"/>
       <c r="DD74" s="7"/>
       <c r="DE74" s="7"/>
@@ -15114,11 +15197,11 @@
       <c r="CU75" s="21"/>
       <c r="CV75" s="21"/>
       <c r="CW75" s="21"/>
-      <c r="CX75" s="30"/>
+      <c r="CX75" s="21"/>
       <c r="CY75" s="30"/>
       <c r="CZ75" s="30"/>
       <c r="DA75" s="30"/>
-      <c r="DB75" s="7"/>
+      <c r="DB75" s="30"/>
       <c r="DC75" s="7"/>
       <c r="DD75" s="7"/>
       <c r="DE75" s="7"/>
@@ -15193,67 +15276,67 @@
       <c r="A76" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="CX76" s="25"/>
       <c r="CY76" s="25"/>
       <c r="CZ76" s="25"/>
       <c r="DA76" s="25"/>
+      <c r="DB76" s="25"/>
     </row>
     <row r="77" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="CX77" s="25"/>
       <c r="CY77" s="25"/>
       <c r="CZ77" s="25"/>
       <c r="DA77" s="25"/>
+      <c r="DB77" s="25"/>
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="CX78" s="25"/>
+        <v>56</v>
+      </c>
       <c r="CY78" s="25"/>
       <c r="CZ78" s="25"/>
       <c r="DA78" s="25"/>
+      <c r="DB78" s="25"/>
     </row>
     <row r="79" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX79" s="25"/>
       <c r="CY79" s="25"/>
       <c r="CZ79" s="25"/>
       <c r="DA79" s="25"/>
+      <c r="DB79" s="25"/>
     </row>
     <row r="80" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CX80" s="25"/>
       <c r="CY80" s="25"/>
       <c r="CZ80" s="25"/>
       <c r="DA80" s="25"/>
+      <c r="DB80" s="25"/>
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="CX81" s="25"/>
+        <v>57</v>
+      </c>
       <c r="CY81" s="25"/>
       <c r="CZ81" s="25"/>
       <c r="DA81" s="25"/>
+      <c r="DB81" s="25"/>
     </row>
     <row r="82" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CX82" s="25"/>
       <c r="CY82" s="25"/>
       <c r="CZ82" s="25"/>
       <c r="DA82" s="25"/>
+      <c r="DB82" s="25"/>
     </row>
     <row r="83" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CX83" s="25"/>
       <c r="CY83" s="25"/>
       <c r="CZ83" s="25"/>
       <c r="DA83" s="25"/>
+      <c r="DB83" s="25"/>
     </row>
     <row r="84" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
@@ -15407,10 +15490,13 @@
       <c r="CU84" s="19"/>
       <c r="CV84" s="19"/>
       <c r="CW84" s="19"/>
-      <c r="CX84" s="26"/>
+      <c r="CX84" s="19" t="s">
+        <v>58</v>
+      </c>
       <c r="CY84" s="26"/>
       <c r="CZ84" s="26"/>
       <c r="DA84" s="26"/>
+      <c r="DB84" s="26"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
@@ -15714,17 +15800,20 @@
       <c r="CW85" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="CX85" s="31"/>
+      <c r="CX85" s="20" t="s">
+        <v>2</v>
+      </c>
       <c r="CY85" s="31"/>
       <c r="CZ85" s="31"/>
       <c r="DA85" s="31"/>
+      <c r="DB85" s="31"/>
     </row>
     <row r="86" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
-      <c r="CX86" s="25"/>
       <c r="CY86" s="25"/>
       <c r="CZ86" s="25"/>
       <c r="DA86" s="25"/>
+      <c r="DB86" s="25"/>
     </row>
     <row r="87" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
@@ -16030,11 +16119,13 @@
       <c r="CW87" s="28">
         <v>-3.9639994905840439</v>
       </c>
-      <c r="CX87" s="29"/>
+      <c r="CX87" s="28">
+        <v>3.40870792053542</v>
+      </c>
       <c r="CY87" s="29"/>
       <c r="CZ87" s="29"/>
       <c r="DA87" s="29"/>
-      <c r="DB87" s="7"/>
+      <c r="DB87" s="29"/>
       <c r="DC87" s="7"/>
       <c r="DD87" s="7"/>
       <c r="DE87" s="7"/>
@@ -16409,11 +16500,13 @@
       <c r="CW88" s="28">
         <v>3.0233598620082631</v>
       </c>
-      <c r="CX88" s="29"/>
+      <c r="CX88" s="28">
+        <v>8.3791865252159425</v>
+      </c>
       <c r="CY88" s="29"/>
       <c r="CZ88" s="29"/>
       <c r="DA88" s="29"/>
-      <c r="DB88" s="7"/>
+      <c r="DB88" s="29"/>
       <c r="DC88" s="7"/>
       <c r="DD88" s="7"/>
       <c r="DE88" s="7"/>
@@ -16788,11 +16881,13 @@
       <c r="CW89" s="28">
         <v>10.735514434225337</v>
       </c>
-      <c r="CX89" s="29"/>
+      <c r="CX89" s="28">
+        <v>15.168662438497861</v>
+      </c>
       <c r="CY89" s="29"/>
       <c r="CZ89" s="29"/>
       <c r="DA89" s="29"/>
-      <c r="DB89" s="7"/>
+      <c r="DB89" s="29"/>
       <c r="DC89" s="7"/>
       <c r="DD89" s="7"/>
       <c r="DE89" s="7"/>
@@ -17167,11 +17262,13 @@
       <c r="CW90" s="28">
         <v>9.6484605524462097</v>
       </c>
-      <c r="CX90" s="29"/>
+      <c r="CX90" s="28">
+        <v>-6.3358217603934719</v>
+      </c>
       <c r="CY90" s="29"/>
       <c r="CZ90" s="29"/>
       <c r="DA90" s="29"/>
-      <c r="DB90" s="7"/>
+      <c r="DB90" s="29"/>
       <c r="DC90" s="7"/>
       <c r="DD90" s="7"/>
       <c r="DE90" s="7"/>
@@ -17546,11 +17643,13 @@
       <c r="CW91" s="28">
         <v>-1.5356912870190627</v>
       </c>
-      <c r="CX91" s="29"/>
+      <c r="CX91" s="28">
+        <v>-4.8330392910218904</v>
+      </c>
       <c r="CY91" s="29"/>
       <c r="CZ91" s="29"/>
       <c r="DA91" s="29"/>
-      <c r="DB91" s="7"/>
+      <c r="DB91" s="29"/>
       <c r="DC91" s="7"/>
       <c r="DD91" s="7"/>
       <c r="DE91" s="7"/>
@@ -17885,11 +17984,13 @@
       <c r="CW92" s="28">
         <v>-11.141257544334167</v>
       </c>
-      <c r="CX92" s="29"/>
+      <c r="CX92" s="28">
+        <v>-12.333784765949346</v>
+      </c>
       <c r="CY92" s="29"/>
       <c r="CZ92" s="29"/>
       <c r="DA92" s="29"/>
-      <c r="DB92" s="7"/>
+      <c r="DB92" s="29"/>
       <c r="DC92" s="7"/>
       <c r="DD92" s="7"/>
       <c r="DE92" s="7"/>
@@ -18224,11 +18325,13 @@
       <c r="CW93" s="28">
         <v>-11.661654607721374</v>
       </c>
-      <c r="CX93" s="29"/>
+      <c r="CX93" s="28">
+        <v>-9.9556352085265871</v>
+      </c>
       <c r="CY93" s="29"/>
       <c r="CZ93" s="29"/>
       <c r="DA93" s="29"/>
-      <c r="DB93" s="7"/>
+      <c r="DB93" s="29"/>
       <c r="DC93" s="7"/>
       <c r="DD93" s="7"/>
       <c r="DE93" s="7"/>
@@ -18603,11 +18706,13 @@
       <c r="CW94" s="28">
         <v>-0.92277891007823598</v>
       </c>
-      <c r="CX94" s="29"/>
+      <c r="CX94" s="28">
+        <v>19.046673330557425</v>
+      </c>
       <c r="CY94" s="29"/>
       <c r="CZ94" s="29"/>
       <c r="DA94" s="29"/>
-      <c r="DB94" s="7"/>
+      <c r="DB94" s="29"/>
       <c r="DC94" s="7"/>
       <c r="DD94" s="7"/>
       <c r="DE94" s="7"/>
@@ -18779,11 +18884,11 @@
       <c r="CU95" s="21"/>
       <c r="CV95" s="21"/>
       <c r="CW95" s="21"/>
-      <c r="CX95" s="30"/>
+      <c r="CX95" s="21"/>
       <c r="CY95" s="30"/>
       <c r="CZ95" s="30"/>
       <c r="DA95" s="30"/>
-      <c r="DB95" s="7"/>
+      <c r="DB95" s="30"/>
       <c r="DC95" s="7"/>
       <c r="DD95" s="7"/>
       <c r="DE95" s="7"/>
@@ -19158,11 +19263,13 @@
       <c r="CW96" s="28">
         <v>3.5653726821629732</v>
       </c>
-      <c r="CX96" s="29"/>
+      <c r="CX96" s="28">
+        <v>4.1955580074689749</v>
+      </c>
       <c r="CY96" s="29"/>
       <c r="CZ96" s="29"/>
       <c r="DA96" s="29"/>
-      <c r="DB96" s="7"/>
+      <c r="DB96" s="29"/>
       <c r="DC96" s="7"/>
       <c r="DD96" s="7"/>
       <c r="DE96" s="7"/>
@@ -19335,19 +19442,20 @@
       <c r="CU97" s="23"/>
       <c r="CV97" s="23"/>
       <c r="CW97" s="23"/>
-      <c r="CX97" s="31"/>
+      <c r="CX97" s="23"/>
       <c r="CY97" s="31"/>
       <c r="CZ97" s="31"/>
       <c r="DA97" s="31"/>
+      <c r="DB97" s="31"/>
     </row>
     <row r="98" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A98" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CX98" s="25"/>
       <c r="CY98" s="25"/>
       <c r="CZ98" s="25"/>
       <c r="DA98" s="25"/>
+      <c r="DB98" s="25"/>
     </row>
     <row r="99" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="7"/>
@@ -19454,7 +19562,7 @@
       <c r="CY99" s="30"/>
       <c r="CZ99" s="30"/>
       <c r="DA99" s="30"/>
-      <c r="DB99" s="7"/>
+      <c r="DB99" s="30"/>
       <c r="DC99" s="7"/>
       <c r="DD99" s="7"/>
       <c r="DE99" s="7"/>
@@ -19630,7 +19738,7 @@
       <c r="CY100" s="21"/>
       <c r="CZ100" s="21"/>
       <c r="DA100" s="21"/>
-      <c r="DB100" s="7"/>
+      <c r="DB100" s="21"/>
       <c r="DC100" s="7"/>
       <c r="DD100" s="7"/>
       <c r="DE100" s="7"/>
@@ -19708,7 +19816,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -19718,7 +19826,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -19884,6 +19992,9 @@
       <c r="CY108" s="19"/>
       <c r="CZ108" s="19"/>
       <c r="DA108" s="19"/>
+      <c r="DB108" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
@@ -20198,6 +20309,9 @@
       </c>
       <c r="DA109" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB109" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20519,7 +20633,9 @@
       <c r="DA111" s="28">
         <v>112.67482589868681</v>
       </c>
-      <c r="DB111" s="7"/>
+      <c r="DB111" s="28">
+        <v>110.61787358554889</v>
+      </c>
       <c r="DC111" s="7"/>
       <c r="DD111" s="7"/>
       <c r="DE111" s="7"/>
@@ -20910,7 +21026,9 @@
       <c r="DA112" s="28">
         <v>119.81180296023084</v>
       </c>
-      <c r="DB112" s="7"/>
+      <c r="DB112" s="28">
+        <v>89.847840851201255</v>
+      </c>
       <c r="DC112" s="7"/>
       <c r="DD112" s="7"/>
       <c r="DE112" s="7"/>
@@ -21301,7 +21419,9 @@
       <c r="DA113" s="28">
         <v>108.21791215555088</v>
       </c>
-      <c r="DB113" s="7"/>
+      <c r="DB113" s="28">
+        <v>130.55164428200879</v>
+      </c>
       <c r="DC113" s="7"/>
       <c r="DD113" s="7"/>
       <c r="DE113" s="7"/>
@@ -21692,7 +21812,9 @@
       <c r="DA114" s="28">
         <v>117.47951955374629</v>
       </c>
-      <c r="DB114" s="7"/>
+      <c r="DB114" s="28">
+        <v>101.00868726806563</v>
+      </c>
       <c r="DC114" s="7"/>
       <c r="DD114" s="7"/>
       <c r="DE114" s="7"/>
@@ -22083,7 +22205,9 @@
       <c r="DA115" s="28">
         <v>121.84481811627602</v>
       </c>
-      <c r="DB115" s="7"/>
+      <c r="DB115" s="28">
+        <v>96.963140221228102</v>
+      </c>
       <c r="DC115" s="7"/>
       <c r="DD115" s="7"/>
       <c r="DE115" s="7"/>
@@ -22474,7 +22598,9 @@
       <c r="DA116" s="28">
         <v>120.52499186465822</v>
       </c>
-      <c r="DB116" s="7"/>
+      <c r="DB116" s="28">
+        <v>95.100186615150434</v>
+      </c>
       <c r="DC116" s="7"/>
       <c r="DD116" s="7"/>
       <c r="DE116" s="7"/>
@@ -22865,7 +22991,9 @@
       <c r="DA117" s="28">
         <v>121.75572216790114</v>
       </c>
-      <c r="DB117" s="7"/>
+      <c r="DB117" s="28">
+        <v>96.402578089174796</v>
+      </c>
       <c r="DC117" s="7"/>
       <c r="DD117" s="7"/>
       <c r="DE117" s="7"/>
@@ -23256,7 +23384,9 @@
       <c r="DA118" s="28">
         <v>123.80018072058554</v>
       </c>
-      <c r="DB118" s="7"/>
+      <c r="DB118" s="28">
+        <v>96.74594462234964</v>
+      </c>
       <c r="DC118" s="7"/>
       <c r="DD118" s="7"/>
       <c r="DE118" s="7"/>
@@ -23436,7 +23566,7 @@
       <c r="CY119" s="21"/>
       <c r="CZ119" s="21"/>
       <c r="DA119" s="21"/>
-      <c r="DB119" s="7"/>
+      <c r="DB119" s="21"/>
       <c r="DC119" s="7"/>
       <c r="DD119" s="7"/>
       <c r="DE119" s="7"/>
@@ -23827,7 +23957,9 @@
       <c r="DA120" s="28">
         <v>112.25393438742854</v>
       </c>
-      <c r="DB120" s="7"/>
+      <c r="DB120" s="28">
+        <v>112.11664185276864</v>
+      </c>
       <c r="DC120" s="7"/>
       <c r="DD120" s="7"/>
       <c r="DE120" s="7"/>
@@ -24008,6 +24140,7 @@
       <c r="CY121" s="23"/>
       <c r="CZ121" s="23"/>
       <c r="DA121" s="23"/>
+      <c r="DB121" s="23"/>
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A122" s="9" t="s">
@@ -24026,7 +24159,7 @@
     </row>
     <row r="127" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
@@ -24036,7 +24169,7 @@
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
@@ -24202,6 +24335,9 @@
       <c r="CY133" s="19"/>
       <c r="CZ133" s="19"/>
       <c r="DA133" s="19"/>
+      <c r="DB133" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
@@ -24516,6 +24652,9 @@
       </c>
       <c r="DA134" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB134" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -24837,7 +24976,9 @@
       <c r="DA136" s="17">
         <v>14.900584508539961</v>
       </c>
-      <c r="DB136" s="7"/>
+      <c r="DB136" s="17">
+        <v>14.795526176149531</v>
+      </c>
       <c r="DC136" s="7"/>
       <c r="DD136" s="7"/>
       <c r="DE136" s="7"/>
@@ -25228,7 +25369,9 @@
       <c r="DA137" s="17">
         <v>2.3074966152800478</v>
       </c>
-      <c r="DB137" s="7"/>
+      <c r="DB137" s="17">
+        <v>4.3924988098370816</v>
+      </c>
       <c r="DC137" s="7"/>
       <c r="DD137" s="7"/>
       <c r="DE137" s="7"/>
@@ -25619,7 +25762,9 @@
       <c r="DA138" s="17">
         <v>57.185115343698754</v>
       </c>
-      <c r="DB138" s="7"/>
+      <c r="DB138" s="17">
+        <v>48.122306060117367</v>
+      </c>
       <c r="DC138" s="7"/>
       <c r="DD138" s="7"/>
       <c r="DE138" s="7"/>
@@ -26010,7 +26155,9 @@
       <c r="DA139" s="17">
         <v>0.96531168716189519</v>
       </c>
-      <c r="DB139" s="7"/>
+      <c r="DB139" s="17">
+        <v>0.95755837650342968</v>
+      </c>
       <c r="DC139" s="7"/>
       <c r="DD139" s="7"/>
       <c r="DE139" s="7"/>
@@ -26401,7 +26548,9 @@
       <c r="DA140" s="17">
         <v>3.5658341166517831</v>
       </c>
-      <c r="DB140" s="7"/>
+      <c r="DB140" s="17">
+        <v>5.5472565495368711</v>
+      </c>
       <c r="DC140" s="7"/>
       <c r="DD140" s="7"/>
       <c r="DE140" s="7"/>
@@ -26792,7 +26941,9 @@
       <c r="DA141" s="17">
         <v>14.012072400911691</v>
       </c>
-      <c r="DB141" s="7"/>
+      <c r="DB141" s="17">
+        <v>18.425910637727767</v>
+      </c>
       <c r="DC141" s="7"/>
       <c r="DD141" s="7"/>
       <c r="DE141" s="7"/>
@@ -27183,7 +27334,9 @@
       <c r="DA142" s="17">
         <v>0.81900559499963554</v>
       </c>
-      <c r="DB142" s="7"/>
+      <c r="DB142" s="17">
+        <v>1.0170321882363593</v>
+      </c>
       <c r="DC142" s="7"/>
       <c r="DD142" s="7"/>
       <c r="DE142" s="7"/>
@@ -27574,7 +27727,9 @@
       <c r="DA143" s="17">
         <v>6.2445797327562484</v>
       </c>
-      <c r="DB143" s="7"/>
+      <c r="DB143" s="17">
+        <v>6.7419112018915932</v>
+      </c>
       <c r="DC143" s="7"/>
       <c r="DD143" s="7"/>
       <c r="DE143" s="7"/>
@@ -27754,7 +27909,7 @@
       <c r="CY144" s="21"/>
       <c r="CZ144" s="21"/>
       <c r="DA144" s="21"/>
-      <c r="DB144" s="7"/>
+      <c r="DB144" s="21"/>
       <c r="DC144" s="7"/>
       <c r="DD144" s="7"/>
       <c r="DE144" s="7"/>
@@ -28145,7 +28300,9 @@
       <c r="DA145" s="28">
         <v>100</v>
       </c>
-      <c r="DB145" s="7"/>
+      <c r="DB145" s="28">
+        <v>100</v>
+      </c>
       <c r="DC145" s="7"/>
       <c r="DD145" s="7"/>
       <c r="DE145" s="7"/>
@@ -28326,6 +28483,7 @@
       <c r="CY146" s="23"/>
       <c r="CZ146" s="23"/>
       <c r="DA146" s="23"/>
+      <c r="DB146" s="23"/>
     </row>
     <row r="147" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A147" s="9" t="s">
@@ -28437,7 +28595,7 @@
       <c r="CY148" s="21"/>
       <c r="CZ148" s="21"/>
       <c r="DA148" s="21"/>
-      <c r="DB148" s="7"/>
+      <c r="DB148" s="21"/>
       <c r="DC148" s="7"/>
       <c r="DD148" s="7"/>
       <c r="DE148" s="7"/>
@@ -28617,7 +28775,7 @@
       <c r="CY149" s="21"/>
       <c r="CZ149" s="21"/>
       <c r="DA149" s="21"/>
-      <c r="DB149" s="7"/>
+      <c r="DB149" s="21"/>
       <c r="DC149" s="7"/>
       <c r="DD149" s="7"/>
       <c r="DE149" s="7"/>
@@ -28704,7 +28862,7 @@
     </row>
     <row r="152" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
@@ -28714,7 +28872,7 @@
     </row>
     <row r="155" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="156" spans="1:179" x14ac:dyDescent="0.2">
@@ -28880,6 +29038,9 @@
       <c r="CY158" s="19"/>
       <c r="CZ158" s="19"/>
       <c r="DA158" s="19"/>
+      <c r="DB158" s="19">
+        <v>2026</v>
+      </c>
     </row>
     <row r="159" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
@@ -29194,6 +29355,9 @@
       </c>
       <c r="DA159" s="15" t="s">
         <v>5</v>
+      </c>
+      <c r="DB159" s="15" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -29515,7 +29679,9 @@
       <c r="DA161" s="17">
         <v>14.844924076119412</v>
       </c>
-      <c r="DB161" s="7"/>
+      <c r="DB161" s="17">
+        <v>14.995991656192253</v>
+      </c>
       <c r="DC161" s="7"/>
       <c r="DD161" s="7"/>
       <c r="DE161" s="7"/>
@@ -29906,7 +30072,9 @@
       <c r="DA162" s="17">
         <v>2.1619370316698956</v>
       </c>
-      <c r="DB162" s="7"/>
+      <c r="DB162" s="17">
+        <v>5.4811803070127123</v>
+      </c>
       <c r="DC162" s="7"/>
       <c r="DD162" s="7"/>
       <c r="DE162" s="7"/>
@@ -30297,7 +30465,9 @@
       <c r="DA163" s="17">
         <v>59.317852819985561</v>
       </c>
-      <c r="DB163" s="7"/>
+      <c r="DB163" s="17">
+        <v>41.32702719558943</v>
+      </c>
       <c r="DC163" s="7"/>
       <c r="DD163" s="7"/>
       <c r="DE163" s="7"/>
@@ -30688,7 +30858,9 @@
       <c r="DA164" s="17">
         <v>0.92237383337710321</v>
       </c>
-      <c r="DB164" s="7"/>
+      <c r="DB164" s="17">
+        <v>1.0628613484168645</v>
+      </c>
       <c r="DC164" s="7"/>
       <c r="DD164" s="7"/>
       <c r="DE164" s="7"/>
@@ -31079,7 +31251,9 @@
       <c r="DA165" s="17">
         <v>3.2851533217038336</v>
       </c>
-      <c r="DB165" s="7"/>
+      <c r="DB165" s="17">
+        <v>6.4141876429625935</v>
+      </c>
       <c r="DC165" s="7"/>
       <c r="DD165" s="7"/>
       <c r="DE165" s="7"/>
@@ -31470,7 +31644,9 @@
       <c r="DA166" s="17">
         <v>13.050490455042851</v>
       </c>
-      <c r="DB166" s="7"/>
+      <c r="DB166" s="17">
+        <v>21.722893480128384</v>
+      </c>
       <c r="DC166" s="7"/>
       <c r="DD166" s="7"/>
       <c r="DE166" s="7"/>
@@ -31861,7 +32037,9 @@
       <c r="DA167" s="17">
         <v>0.75509059194150552</v>
       </c>
-      <c r="DB167" s="7"/>
+      <c r="DB167" s="17">
+        <v>1.1828131141446898</v>
+      </c>
       <c r="DC167" s="7"/>
       <c r="DD167" s="7"/>
       <c r="DE167" s="7"/>
@@ -32252,7 +32430,9 @@
       <c r="DA168" s="17">
         <v>5.6621778701598204</v>
       </c>
-      <c r="DB168" s="7"/>
+      <c r="DB168" s="17">
+        <v>7.8130452555530683</v>
+      </c>
       <c r="DC168" s="7"/>
       <c r="DD168" s="7"/>
       <c r="DE168" s="7"/>
@@ -32432,7 +32612,7 @@
       <c r="CY169" s="21"/>
       <c r="CZ169" s="21"/>
       <c r="DA169" s="21"/>
-      <c r="DB169" s="7"/>
+      <c r="DB169" s="21"/>
       <c r="DC169" s="7"/>
       <c r="DD169" s="7"/>
       <c r="DE169" s="7"/>
@@ -32823,7 +33003,9 @@
       <c r="DA170" s="28">
         <v>100</v>
       </c>
-      <c r="DB170" s="7"/>
+      <c r="DB170" s="28">
+        <v>100</v>
+      </c>
       <c r="DC170" s="7"/>
       <c r="DD170" s="7"/>
       <c r="DE170" s="7"/>
@@ -33004,6 +33186,7 @@
       <c r="CY171" s="23"/>
       <c r="CZ171" s="23"/>
       <c r="DA171" s="23"/>
+      <c r="DB171" s="23"/>
     </row>
     <row r="172" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A172" s="9" t="s">
@@ -33116,7 +33299,7 @@
       <c r="CY173" s="32"/>
       <c r="CZ173" s="32"/>
       <c r="DA173" s="32"/>
-      <c r="DB173" s="12"/>
+      <c r="DB173" s="32"/>
       <c r="DC173" s="12"/>
       <c r="DD173" s="12"/>
       <c r="DE173" s="12"/>
@@ -33196,9 +33379,9 @@
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="50" max="81" man="1"/>
-    <brk id="100" max="81" man="1"/>
-    <brk id="124" max="81" man="1"/>
+    <brk id="50" max="105" man="1"/>
+    <brk id="100" max="105" man="1"/>
+    <brk id="124" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-07IOS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-07IOS_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1783EFDD-1A71-4534-B669-3BD4849ADB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D36790-FC31-446B-9C81-F37B4CF31D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -359,7 +359,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">IOS!$A$1:$DB$173</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">IOS!$A$1:$DC$173</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="59">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -703,13 +703,13 @@
     <t>Table 8.2.7 Imports of Services</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1226,8 +1226,8 @@
   <cols>
     <col min="1" max="1" width="54.85546875" style="1" customWidth="1"/>
     <col min="2" max="93" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="94" max="106" width="15" style="18" bestFit="1" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="1"/>
+    <col min="94" max="107" width="15" style="18" bestFit="1" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" x14ac:dyDescent="0.2">
@@ -1242,7 +1242,7 @@
     </row>
     <row r="3" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:179" x14ac:dyDescent="0.2">
@@ -1252,7 +1252,7 @@
     </row>
     <row r="6" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:179" x14ac:dyDescent="0.2">
@@ -1421,6 +1421,7 @@
       <c r="DB9" s="19">
         <v>2026</v>
       </c>
+      <c r="DC9" s="19"/>
     </row>
     <row r="10" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
@@ -1738,6 +1739,9 @@
       </c>
       <c r="DB10" s="20" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="20" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2060,9 +2064,11 @@
         <v>98645.294929158903</v>
       </c>
       <c r="DB12" s="14">
-        <v>99602.591382005063</v>
-      </c>
-      <c r="DC12" s="7"/>
+        <v>96328.765933552335</v>
+      </c>
+      <c r="DC12" s="14">
+        <v>128578.05266254088</v>
+      </c>
       <c r="DD12" s="7"/>
       <c r="DE12" s="7"/>
       <c r="DF12" s="7"/>
@@ -2453,9 +2459,11 @@
         <v>15276.158061576607</v>
       </c>
       <c r="DB13" s="14">
-        <v>29570.037516300414</v>
-      </c>
-      <c r="DC13" s="7"/>
+        <v>29570.315540941065</v>
+      </c>
+      <c r="DC13" s="14">
+        <v>45819.732243843297</v>
+      </c>
       <c r="DD13" s="7"/>
       <c r="DE13" s="7"/>
       <c r="DF13" s="7"/>
@@ -2848,7 +2856,9 @@
       <c r="DB14" s="14">
         <v>323956.46696176101</v>
       </c>
-      <c r="DC14" s="7"/>
+      <c r="DC14" s="14">
+        <v>236911.2904918979</v>
+      </c>
       <c r="DD14" s="7"/>
       <c r="DE14" s="7"/>
       <c r="DF14" s="7"/>
@@ -3239,9 +3249,11 @@
         <v>6390.5852836896293</v>
       </c>
       <c r="DB15" s="14">
-        <v>6446.225336212291</v>
-      </c>
-      <c r="DC15" s="7"/>
+        <v>6537.1308630618632</v>
+      </c>
+      <c r="DC15" s="14">
+        <v>6354.6477470636846</v>
+      </c>
       <c r="DD15" s="7"/>
       <c r="DE15" s="7"/>
       <c r="DF15" s="7"/>
@@ -3632,9 +3644,11 @@
         <v>23606.641598789109</v>
       </c>
       <c r="DB16" s="14">
-        <v>37343.797092214227</v>
-      </c>
-      <c r="DC16" s="7"/>
+        <v>36416.276769047246</v>
+      </c>
+      <c r="DC16" s="14">
+        <v>37302.001466071255</v>
+      </c>
       <c r="DD16" s="7"/>
       <c r="DE16" s="7"/>
       <c r="DF16" s="7"/>
@@ -4025,9 +4039,11 @@
         <v>92763.140517371517</v>
       </c>
       <c r="DB17" s="14">
-        <v>124042.12099258775</v>
-      </c>
-      <c r="DC17" s="7"/>
+        <v>128822.14094081178</v>
+      </c>
+      <c r="DC17" s="14">
+        <v>118662.70507713778</v>
+      </c>
       <c r="DD17" s="7"/>
       <c r="DE17" s="7"/>
       <c r="DF17" s="7"/>
@@ -4418,9 +4434,11 @@
         <v>5422.0053193931162</v>
       </c>
       <c r="DB18" s="14">
-        <v>6846.5994558914144</v>
-      </c>
-      <c r="DC18" s="7"/>
+        <v>8262.571306696962</v>
+      </c>
+      <c r="DC18" s="14">
+        <v>8289.6200366730154</v>
+      </c>
       <c r="DD18" s="7"/>
       <c r="DE18" s="7"/>
       <c r="DF18" s="7"/>
@@ -4811,9 +4829,11 @@
         <v>41340.553391938534</v>
       </c>
       <c r="DB19" s="14">
-        <v>45386.14028193547</v>
-      </c>
-      <c r="DC19" s="7"/>
+        <v>45579.719157673549</v>
+      </c>
+      <c r="DC19" s="14">
+        <v>57289.692437422484</v>
+      </c>
       <c r="DD19" s="7"/>
       <c r="DE19" s="7"/>
       <c r="DF19" s="7"/>
@@ -4993,7 +5013,7 @@
       <c r="CZ20" s="21"/>
       <c r="DA20" s="21"/>
       <c r="DB20" s="21"/>
-      <c r="DC20" s="7"/>
+      <c r="DC20" s="21"/>
       <c r="DD20" s="7"/>
       <c r="DE20" s="7"/>
       <c r="DF20" s="7"/>
@@ -5384,9 +5404,11 @@
         <v>662022.98891444434</v>
       </c>
       <c r="DB21" s="22">
-        <v>673193.97901890764</v>
-      </c>
-      <c r="DC21" s="7"/>
+        <v>675473.38747354574</v>
+      </c>
+      <c r="DC21" s="22">
+        <v>639207.74216265022</v>
+      </c>
       <c r="DD21" s="7"/>
       <c r="DE21" s="7"/>
       <c r="DF21" s="7"/>
@@ -5567,6 +5589,7 @@
       <c r="CZ22" s="23"/>
       <c r="DA22" s="23"/>
       <c r="DB22" s="23"/>
+      <c r="DC22" s="23"/>
     </row>
     <row r="23" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
@@ -5679,7 +5702,7 @@
       <c r="CZ24" s="21"/>
       <c r="DA24" s="21"/>
       <c r="DB24" s="21"/>
-      <c r="DC24" s="7"/>
+      <c r="DC24" s="21"/>
       <c r="DD24" s="7"/>
       <c r="DE24" s="7"/>
       <c r="DF24" s="7"/>
@@ -5859,7 +5882,7 @@
       <c r="CZ25" s="21"/>
       <c r="DA25" s="21"/>
       <c r="DB25" s="21"/>
-      <c r="DC25" s="7"/>
+      <c r="DC25" s="21"/>
       <c r="DD25" s="7"/>
       <c r="DE25" s="7"/>
       <c r="DF25" s="7"/>
@@ -5945,7 +5968,7 @@
     </row>
     <row r="28" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:179" x14ac:dyDescent="0.2">
@@ -5955,7 +5978,7 @@
     </row>
     <row r="31" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:179" x14ac:dyDescent="0.2">
@@ -6124,6 +6147,7 @@
       <c r="DB34" s="19">
         <v>2026</v>
       </c>
+      <c r="DC34" s="19"/>
     </row>
     <row r="35" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
@@ -6441,6 +6465,9 @@
       </c>
       <c r="DB35" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC35" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -6763,9 +6790,11 @@
         <v>87548.65529400263</v>
       </c>
       <c r="DB37" s="14">
-        <v>90042.041266482222</v>
-      </c>
-      <c r="DC37" s="7"/>
+        <v>87089.331801912456</v>
+      </c>
+      <c r="DC37" s="14">
+        <v>103073.56925559578</v>
+      </c>
       <c r="DD37" s="7"/>
       <c r="DE37" s="7"/>
       <c r="DF37" s="7"/>
@@ -7156,9 +7185,11 @@
         <v>12750.127853970469</v>
       </c>
       <c r="DB38" s="14">
-        <v>32911.238863571496</v>
-      </c>
-      <c r="DC38" s="7"/>
+        <v>32911.548302994881</v>
+      </c>
+      <c r="DC38" s="14">
+        <v>33963.93885036002</v>
+      </c>
       <c r="DD38" s="7"/>
       <c r="DE38" s="7"/>
       <c r="DF38" s="7"/>
@@ -7551,7 +7582,9 @@
       <c r="DB39" s="14">
         <v>248144.30238961388</v>
       </c>
-      <c r="DC39" s="7"/>
+      <c r="DC39" s="14">
+        <v>176377.97638282864</v>
+      </c>
       <c r="DD39" s="7"/>
       <c r="DE39" s="7"/>
       <c r="DF39" s="7"/>
@@ -7942,9 +7975,11 @@
         <v>5439.7441426085916</v>
       </c>
       <c r="DB40" s="14">
-        <v>6381.8524035509326</v>
-      </c>
-      <c r="DC40" s="7"/>
+        <v>6471.8501347444089</v>
+      </c>
+      <c r="DC40" s="14">
+        <v>5056.3714026940788</v>
+      </c>
       <c r="DD40" s="7"/>
       <c r="DE40" s="7"/>
       <c r="DF40" s="7"/>
@@ -8335,9 +8370,11 @@
         <v>19374.350065721621</v>
       </c>
       <c r="DB41" s="14">
-        <v>38513.394891101685</v>
-      </c>
-      <c r="DC41" s="7"/>
+        <v>37556.82487794949</v>
+      </c>
+      <c r="DC41" s="14">
+        <v>28650.099058041844</v>
+      </c>
       <c r="DD41" s="7"/>
       <c r="DE41" s="7"/>
       <c r="DF41" s="7"/>
@@ -8728,9 +8765,11 @@
         <v>76965.896518407186</v>
       </c>
       <c r="DB42" s="14">
-        <v>130433.09945811037</v>
-      </c>
-      <c r="DC42" s="7"/>
+        <v>135459.39868880244</v>
+      </c>
+      <c r="DC42" s="14">
+        <v>92548.9361749542</v>
+      </c>
       <c r="DD42" s="7"/>
       <c r="DE42" s="7"/>
       <c r="DF42" s="7"/>
@@ -9121,9 +9160,11 @@
         <v>4453.1831628546961</v>
       </c>
       <c r="DB43" s="14">
-        <v>7102.0916572979395</v>
-      </c>
-      <c r="DC43" s="7"/>
+        <v>8570.9028435462351</v>
+      </c>
+      <c r="DC43" s="14">
+        <v>6350.2346669853723</v>
+      </c>
       <c r="DD43" s="7"/>
       <c r="DE43" s="7"/>
       <c r="DF43" s="7"/>
@@ -9514,9 +9555,11 @@
         <v>33392.966917587393</v>
       </c>
       <c r="DB44" s="14">
-        <v>46912.705704721244</v>
-      </c>
-      <c r="DC44" s="7"/>
+        <v>47112.795617010299</v>
+      </c>
+      <c r="DC44" s="14">
+        <v>43358.431264433755</v>
+      </c>
       <c r="DD44" s="7"/>
       <c r="DE44" s="7"/>
       <c r="DF44" s="7"/>
@@ -9696,7 +9739,7 @@
       <c r="CZ45" s="21"/>
       <c r="DA45" s="21"/>
       <c r="DB45" s="21"/>
-      <c r="DC45" s="7"/>
+      <c r="DC45" s="21"/>
       <c r="DD45" s="7"/>
       <c r="DE45" s="7"/>
       <c r="DF45" s="7"/>
@@ -10087,9 +10130,11 @@
         <v>589754.82020039123</v>
       </c>
       <c r="DB46" s="22">
-        <v>600440.72663444979</v>
-      </c>
-      <c r="DC46" s="7"/>
+        <v>603316.95465657418</v>
+      </c>
+      <c r="DC46" s="22">
+        <v>489379.5570558937</v>
+      </c>
       <c r="DD46" s="7"/>
       <c r="DE46" s="7"/>
       <c r="DF46" s="7"/>
@@ -10270,6 +10315,7 @@
       <c r="CZ47" s="23"/>
       <c r="DA47" s="23"/>
       <c r="DB47" s="23"/>
+      <c r="DC47" s="23"/>
     </row>
     <row r="48" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
@@ -10382,7 +10428,7 @@
       <c r="CZ49" s="21"/>
       <c r="DA49" s="21"/>
       <c r="DB49" s="21"/>
-      <c r="DC49" s="7"/>
+      <c r="DC49" s="21"/>
       <c r="DD49" s="7"/>
       <c r="DE49" s="7"/>
       <c r="DF49" s="7"/>
@@ -10562,7 +10608,7 @@
       <c r="CZ50" s="21"/>
       <c r="DA50" s="21"/>
       <c r="DB50" s="21"/>
-      <c r="DC50" s="7"/>
+      <c r="DC50" s="21"/>
       <c r="DD50" s="7"/>
       <c r="DE50" s="7"/>
       <c r="DF50" s="7"/>
@@ -10648,7 +10694,7 @@
     </row>
     <row r="53" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:179" x14ac:dyDescent="0.2">
@@ -10665,6 +10711,7 @@
       <c r="CZ54" s="24"/>
       <c r="DA54" s="24"/>
       <c r="DB54" s="24"/>
+      <c r="DC54" s="24"/>
     </row>
     <row r="55" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
@@ -10683,10 +10730,11 @@
       <c r="CZ55" s="24"/>
       <c r="DA55" s="24"/>
       <c r="DB55" s="24"/>
+      <c r="DC55" s="24"/>
     </row>
     <row r="56" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="CP56" s="24"/>
       <c r="CQ56" s="24"/>
@@ -10701,6 +10749,7 @@
       <c r="CZ56" s="24"/>
       <c r="DA56" s="24"/>
       <c r="DB56" s="24"/>
+      <c r="DC56" s="24"/>
     </row>
     <row r="57" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
@@ -10713,13 +10762,13 @@
       <c r="CZ57" s="25"/>
       <c r="DA57" s="25"/>
       <c r="DB57" s="25"/>
+      <c r="DC57" s="25"/>
     </row>
     <row r="58" spans="1:179" x14ac:dyDescent="0.2">
-      <c r="CX58" s="25"/>
-      <c r="CY58" s="25"/>
       <c r="CZ58" s="25"/>
       <c r="DA58" s="25"/>
       <c r="DB58" s="25"/>
+      <c r="DC58" s="25"/>
     </row>
     <row r="59" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
@@ -10874,12 +10923,13 @@
       <c r="CV59" s="19"/>
       <c r="CW59" s="19"/>
       <c r="CX59" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="CY59" s="26"/>
+        <v>56</v>
+      </c>
+      <c r="CY59" s="19"/>
       <c r="CZ59" s="26"/>
       <c r="DA59" s="26"/>
       <c r="DB59" s="26"/>
+      <c r="DC59" s="26"/>
     </row>
     <row r="60" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
@@ -11186,17 +11236,20 @@
       <c r="CX60" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="CY60" s="27"/>
+      <c r="CY60" s="15" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ60" s="27"/>
       <c r="DA60" s="27"/>
       <c r="DB60" s="27"/>
+      <c r="DC60" s="27"/>
     </row>
     <row r="61" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6"/>
-      <c r="CY61" s="25"/>
       <c r="CZ61" s="25"/>
       <c r="DA61" s="25"/>
       <c r="DB61" s="25"/>
+      <c r="DC61" s="25"/>
     </row>
     <row r="62" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
@@ -11503,13 +11556,15 @@
         <v>-1.3858175040016363</v>
       </c>
       <c r="CX62" s="28">
-        <v>4.5849926268554384</v>
-      </c>
-      <c r="CY62" s="29"/>
+        <v>1.1474012385464363</v>
+      </c>
+      <c r="CY62" s="28">
+        <v>14.785273836019485</v>
+      </c>
       <c r="CZ62" s="29"/>
       <c r="DA62" s="29"/>
       <c r="DB62" s="29"/>
-      <c r="DC62" s="7"/>
+      <c r="DC62" s="29"/>
       <c r="DD62" s="7"/>
       <c r="DE62" s="7"/>
       <c r="DF62" s="7"/>
@@ -11884,13 +11939,15 @@
         <v>4.9990338676024351</v>
       </c>
       <c r="CX63" s="28">
-        <v>9.7084702155510172</v>
-      </c>
-      <c r="CY63" s="29"/>
+        <v>9.7095017211076424</v>
+      </c>
+      <c r="CY63" s="28">
+        <v>11.671889857169049</v>
+      </c>
       <c r="CZ63" s="29"/>
       <c r="DA63" s="29"/>
       <c r="DB63" s="29"/>
-      <c r="DC63" s="7"/>
+      <c r="DC63" s="29"/>
       <c r="DD63" s="7"/>
       <c r="DE63" s="7"/>
       <c r="DF63" s="7"/>
@@ -12267,11 +12324,13 @@
       <c r="CX64" s="28">
         <v>16.69893263503279</v>
       </c>
-      <c r="CY64" s="29"/>
+      <c r="CY64" s="28">
+        <v>6.9149696669442875</v>
+      </c>
       <c r="CZ64" s="29"/>
       <c r="DA64" s="29"/>
       <c r="DB64" s="29"/>
-      <c r="DC64" s="7"/>
+      <c r="DC64" s="29"/>
       <c r="DD64" s="7"/>
       <c r="DE64" s="7"/>
       <c r="DF64" s="7"/>
@@ -12646,13 +12705,15 @@
         <v>11.751183794602582</v>
       </c>
       <c r="CX65" s="28">
-        <v>-5.1870194073367202</v>
-      </c>
-      <c r="CY65" s="29"/>
+        <v>-3.8499541476821832</v>
+      </c>
+      <c r="CY65" s="28">
+        <v>-3.086360559678397</v>
+      </c>
       <c r="CZ65" s="29"/>
       <c r="DA65" s="29"/>
       <c r="DB65" s="29"/>
-      <c r="DC65" s="7"/>
+      <c r="DC65" s="29"/>
       <c r="DD65" s="7"/>
       <c r="DE65" s="7"/>
       <c r="DF65" s="7"/>
@@ -13027,13 +13088,15 @@
         <v>0.35255401446983115</v>
       </c>
       <c r="CX66" s="28">
-        <v>-3.665805131169904</v>
-      </c>
-      <c r="CY66" s="29"/>
+        <v>-6.0584896066164902</v>
+      </c>
+      <c r="CY66" s="28">
+        <v>-2.6723887036195606</v>
+      </c>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
       <c r="DB66" s="29"/>
-      <c r="DC66" s="7"/>
+      <c r="DC66" s="29"/>
       <c r="DD66" s="7"/>
       <c r="DE66" s="7"/>
       <c r="DF66" s="7"/>
@@ -13408,13 +13471,15 @@
         <v>-9.2692013425291861</v>
       </c>
       <c r="CX67" s="28">
-        <v>-11.258548146813879</v>
-      </c>
-      <c r="CY67" s="29"/>
+        <v>-7.8388556528590243</v>
+      </c>
+      <c r="CY67" s="28">
+        <v>-0.28308885088799229</v>
+      </c>
       <c r="CZ67" s="29"/>
       <c r="DA67" s="29"/>
       <c r="DB67" s="29"/>
-      <c r="DC67" s="7"/>
+      <c r="DC67" s="29"/>
       <c r="DD67" s="7"/>
       <c r="DE67" s="7"/>
       <c r="DF67" s="7"/>
@@ -13789,13 +13854,15 @@
         <v>-9.9675944166881152</v>
       </c>
       <c r="CX68" s="28">
-        <v>-8.8512303005229853</v>
-      </c>
-      <c r="CY68" s="29"/>
+        <v>9.9996011175409052</v>
+      </c>
+      <c r="CY68" s="28">
+        <v>35.756979735644279</v>
+      </c>
       <c r="CZ68" s="29"/>
       <c r="DA68" s="29"/>
       <c r="DB68" s="29"/>
-      <c r="DC68" s="7"/>
+      <c r="DC68" s="29"/>
       <c r="DD68" s="7"/>
       <c r="DE68" s="7"/>
       <c r="DF68" s="7"/>
@@ -14170,13 +14237,15 @@
         <v>0.97722018251640463</v>
       </c>
       <c r="CX69" s="28">
-        <v>20.506795022928088</v>
-      </c>
-      <c r="CY69" s="29"/>
+        <v>21.020775056357451</v>
+      </c>
+      <c r="CY69" s="28">
+        <v>41.247616130945971</v>
+      </c>
       <c r="CZ69" s="29"/>
       <c r="DA69" s="29"/>
       <c r="DB69" s="29"/>
-      <c r="DC69" s="7"/>
+      <c r="DC69" s="29"/>
       <c r="DD69" s="7"/>
       <c r="DE69" s="7"/>
       <c r="DF69" s="7"/>
@@ -14348,11 +14417,11 @@
       <c r="CV70" s="21"/>
       <c r="CW70" s="21"/>
       <c r="CX70" s="21"/>
-      <c r="CY70" s="30"/>
+      <c r="CY70" s="21"/>
       <c r="CZ70" s="30"/>
       <c r="DA70" s="30"/>
       <c r="DB70" s="30"/>
-      <c r="DC70" s="7"/>
+      <c r="DC70" s="30"/>
       <c r="DD70" s="7"/>
       <c r="DE70" s="7"/>
       <c r="DF70" s="7"/>
@@ -14727,13 +14796,15 @@
         <v>5.5660199015695326</v>
       </c>
       <c r="CX71" s="28">
-        <v>6.8042011803768503</v>
-      </c>
-      <c r="CY71" s="29"/>
+        <v>7.165836023748767</v>
+      </c>
+      <c r="CY71" s="28">
+        <v>9.2318954642588693</v>
+      </c>
       <c r="CZ71" s="29"/>
       <c r="DA71" s="29"/>
       <c r="DB71" s="29"/>
-      <c r="DC71" s="7"/>
+      <c r="DC71" s="29"/>
       <c r="DD71" s="7"/>
       <c r="DE71" s="7"/>
       <c r="DF71" s="7"/>
@@ -14906,19 +14977,20 @@
       <c r="CV72" s="23"/>
       <c r="CW72" s="23"/>
       <c r="CX72" s="23"/>
-      <c r="CY72" s="31"/>
+      <c r="CY72" s="23"/>
       <c r="CZ72" s="31"/>
       <c r="DA72" s="31"/>
       <c r="DB72" s="31"/>
+      <c r="DC72" s="31"/>
     </row>
     <row r="73" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A73" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CY73" s="25"/>
       <c r="CZ73" s="25"/>
       <c r="DA73" s="25"/>
       <c r="DB73" s="25"/>
+      <c r="DC73" s="25"/>
     </row>
     <row r="74" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="7"/>
@@ -15022,11 +15094,11 @@
       <c r="CV74" s="21"/>
       <c r="CW74" s="21"/>
       <c r="CX74" s="21"/>
-      <c r="CY74" s="30"/>
+      <c r="CY74" s="21"/>
       <c r="CZ74" s="30"/>
       <c r="DA74" s="30"/>
       <c r="DB74" s="30"/>
-      <c r="DC74" s="7"/>
+      <c r="DC74" s="30"/>
       <c r="DD74" s="7"/>
       <c r="DE74" s="7"/>
       <c r="DF74" s="7"/>
@@ -15198,11 +15270,11 @@
       <c r="CV75" s="21"/>
       <c r="CW75" s="21"/>
       <c r="CX75" s="21"/>
-      <c r="CY75" s="30"/>
+      <c r="CY75" s="21"/>
       <c r="CZ75" s="30"/>
       <c r="DA75" s="30"/>
       <c r="DB75" s="30"/>
-      <c r="DC75" s="7"/>
+      <c r="DC75" s="30"/>
       <c r="DD75" s="7"/>
       <c r="DE75" s="7"/>
       <c r="DF75" s="7"/>
@@ -15276,67 +15348,67 @@
       <c r="A76" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="CY76" s="25"/>
       <c r="CZ76" s="25"/>
       <c r="DA76" s="25"/>
       <c r="DB76" s="25"/>
+      <c r="DC76" s="25"/>
     </row>
     <row r="77" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="CY77" s="25"/>
       <c r="CZ77" s="25"/>
       <c r="DA77" s="25"/>
       <c r="DB77" s="25"/>
+      <c r="DC77" s="25"/>
     </row>
     <row r="78" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="CY78" s="25"/>
+        <v>57</v>
+      </c>
       <c r="CZ78" s="25"/>
       <c r="DA78" s="25"/>
       <c r="DB78" s="25"/>
+      <c r="DC78" s="25"/>
     </row>
     <row r="79" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY79" s="25"/>
       <c r="CZ79" s="25"/>
       <c r="DA79" s="25"/>
       <c r="DB79" s="25"/>
+      <c r="DC79" s="25"/>
     </row>
     <row r="80" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CY80" s="25"/>
       <c r="CZ80" s="25"/>
       <c r="DA80" s="25"/>
       <c r="DB80" s="25"/>
+      <c r="DC80" s="25"/>
     </row>
     <row r="81" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="CY81" s="25"/>
+        <v>58</v>
+      </c>
       <c r="CZ81" s="25"/>
       <c r="DA81" s="25"/>
       <c r="DB81" s="25"/>
+      <c r="DC81" s="25"/>
     </row>
     <row r="82" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="CY82" s="25"/>
       <c r="CZ82" s="25"/>
       <c r="DA82" s="25"/>
       <c r="DB82" s="25"/>
+      <c r="DC82" s="25"/>
     </row>
     <row r="83" spans="1:175" x14ac:dyDescent="0.2">
-      <c r="CY83" s="25"/>
       <c r="CZ83" s="25"/>
       <c r="DA83" s="25"/>
       <c r="DB83" s="25"/>
+      <c r="DC83" s="25"/>
     </row>
     <row r="84" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
@@ -15491,12 +15563,13 @@
       <c r="CV84" s="19"/>
       <c r="CW84" s="19"/>
       <c r="CX84" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="CY84" s="26"/>
+        <v>56</v>
+      </c>
+      <c r="CY84" s="19"/>
       <c r="CZ84" s="26"/>
       <c r="DA84" s="26"/>
       <c r="DB84" s="26"/>
+      <c r="DC84" s="26"/>
     </row>
     <row r="85" spans="1:175" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
@@ -15803,17 +15876,20 @@
       <c r="CX85" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="CY85" s="31"/>
+      <c r="CY85" s="20" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ85" s="31"/>
       <c r="DA85" s="31"/>
       <c r="DB85" s="31"/>
+      <c r="DC85" s="31"/>
     </row>
     <row r="86" spans="1:175" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6"/>
-      <c r="CY86" s="25"/>
       <c r="CZ86" s="25"/>
       <c r="DA86" s="25"/>
       <c r="DB86" s="25"/>
+      <c r="DC86" s="25"/>
     </row>
     <row r="87" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
@@ -16120,13 +16196,15 @@
         <v>-3.9639994905840439</v>
       </c>
       <c r="CX87" s="28">
-        <v>3.40870792053542</v>
-      </c>
-      <c r="CY87" s="29"/>
+        <v>1.7671174797470712E-2</v>
+      </c>
+      <c r="CY87" s="28">
+        <v>9.2312871276374722</v>
+      </c>
       <c r="CZ87" s="29"/>
       <c r="DA87" s="29"/>
       <c r="DB87" s="29"/>
-      <c r="DC87" s="7"/>
+      <c r="DC87" s="29"/>
       <c r="DD87" s="7"/>
       <c r="DE87" s="7"/>
       <c r="DF87" s="7"/>
@@ -16501,13 +16579,15 @@
         <v>3.0233598620082631</v>
       </c>
       <c r="CX88" s="28">
-        <v>8.3791865252159425</v>
-      </c>
-      <c r="CY88" s="29"/>
+        <v>8.3802055325260056</v>
+      </c>
+      <c r="CY88" s="28">
+        <v>9.4559358652670937</v>
+      </c>
       <c r="CZ88" s="29"/>
       <c r="DA88" s="29"/>
       <c r="DB88" s="29"/>
-      <c r="DC88" s="7"/>
+      <c r="DC88" s="29"/>
       <c r="DD88" s="7"/>
       <c r="DE88" s="7"/>
       <c r="DF88" s="7"/>
@@ -16884,11 +16964,13 @@
       <c r="CX89" s="28">
         <v>15.168662438497861</v>
       </c>
-      <c r="CY89" s="29"/>
+      <c r="CY89" s="28">
+        <v>4.7439428105359127</v>
+      </c>
       <c r="CZ89" s="29"/>
       <c r="DA89" s="29"/>
       <c r="DB89" s="29"/>
-      <c r="DC89" s="7"/>
+      <c r="DC89" s="29"/>
       <c r="DD89" s="7"/>
       <c r="DE89" s="7"/>
       <c r="DF89" s="7"/>
@@ -17263,13 +17345,15 @@
         <v>9.6484605524462097</v>
       </c>
       <c r="CX90" s="28">
-        <v>-6.3358217603934719</v>
-      </c>
-      <c r="CY90" s="29"/>
+        <v>-5.0149570642786614</v>
+      </c>
+      <c r="CY90" s="28">
+        <v>-5.0094601549499203</v>
+      </c>
       <c r="CZ90" s="29"/>
       <c r="DA90" s="29"/>
       <c r="DB90" s="29"/>
-      <c r="DC90" s="7"/>
+      <c r="DC90" s="29"/>
       <c r="DD90" s="7"/>
       <c r="DE90" s="7"/>
       <c r="DF90" s="7"/>
@@ -17644,13 +17728,15 @@
         <v>-1.5356912870190627</v>
       </c>
       <c r="CX91" s="28">
-        <v>-4.8330392910218904</v>
-      </c>
-      <c r="CY91" s="29"/>
+        <v>-7.1967327829730436</v>
+      </c>
+      <c r="CY91" s="28">
+        <v>-4.6037029228948683</v>
+      </c>
       <c r="CZ91" s="29"/>
       <c r="DA91" s="29"/>
       <c r="DB91" s="29"/>
-      <c r="DC91" s="7"/>
+      <c r="DC91" s="29"/>
       <c r="DD91" s="7"/>
       <c r="DE91" s="7"/>
       <c r="DF91" s="7"/>
@@ -17985,13 +18071,15 @@
         <v>-11.141257544334167</v>
       </c>
       <c r="CX92" s="28">
-        <v>-12.333784765949346</v>
-      </c>
-      <c r="CY92" s="29"/>
+        <v>-8.9555270076101152</v>
+      </c>
+      <c r="CY92" s="28">
+        <v>-2.2618149887157699</v>
+      </c>
       <c r="CZ92" s="29"/>
       <c r="DA92" s="29"/>
       <c r="DB92" s="29"/>
-      <c r="DC92" s="7"/>
+      <c r="DC92" s="29"/>
       <c r="DD92" s="7"/>
       <c r="DE92" s="7"/>
       <c r="DF92" s="7"/>
@@ -18326,13 +18414,15 @@
         <v>-11.661654607721374</v>
       </c>
       <c r="CX93" s="28">
-        <v>-9.9556352085265871</v>
-      </c>
-      <c r="CY93" s="29"/>
+        <v>8.6667899369491153</v>
+      </c>
+      <c r="CY93" s="28">
+        <v>33.063094805797391</v>
+      </c>
       <c r="CZ93" s="29"/>
       <c r="DA93" s="29"/>
       <c r="DB93" s="29"/>
-      <c r="DC93" s="7"/>
+      <c r="DC93" s="29"/>
       <c r="DD93" s="7"/>
       <c r="DE93" s="7"/>
       <c r="DF93" s="7"/>
@@ -18707,13 +18797,15 @@
         <v>-0.92277891007823598</v>
       </c>
       <c r="CX94" s="28">
-        <v>19.046673330557425</v>
-      </c>
-      <c r="CY94" s="29"/>
+        <v>19.55442572017536</v>
+      </c>
+      <c r="CY94" s="28">
+        <v>38.444778109557234</v>
+      </c>
       <c r="CZ94" s="29"/>
       <c r="DA94" s="29"/>
       <c r="DB94" s="29"/>
-      <c r="DC94" s="7"/>
+      <c r="DC94" s="29"/>
       <c r="DD94" s="7"/>
       <c r="DE94" s="7"/>
       <c r="DF94" s="7"/>
@@ -18885,11 +18977,11 @@
       <c r="CV95" s="21"/>
       <c r="CW95" s="21"/>
       <c r="CX95" s="21"/>
-      <c r="CY95" s="30"/>
+      <c r="CY95" s="21"/>
       <c r="CZ95" s="30"/>
       <c r="DA95" s="30"/>
       <c r="DB95" s="30"/>
-      <c r="DC95" s="7"/>
+      <c r="DC95" s="30"/>
       <c r="DD95" s="7"/>
       <c r="DE95" s="7"/>
       <c r="DF95" s="7"/>
@@ -19264,13 +19356,15 @@
         <v>3.5653726821629732</v>
       </c>
       <c r="CX96" s="28">
-        <v>4.1955580074689749</v>
-      </c>
-      <c r="CY96" s="29"/>
+        <v>4.6946750234012171</v>
+      </c>
+      <c r="CY96" s="28">
+        <v>6.4055744130520935</v>
+      </c>
       <c r="CZ96" s="29"/>
       <c r="DA96" s="29"/>
       <c r="DB96" s="29"/>
-      <c r="DC96" s="7"/>
+      <c r="DC96" s="29"/>
       <c r="DD96" s="7"/>
       <c r="DE96" s="7"/>
       <c r="DF96" s="7"/>
@@ -19443,19 +19537,20 @@
       <c r="CV97" s="23"/>
       <c r="CW97" s="23"/>
       <c r="CX97" s="23"/>
-      <c r="CY97" s="31"/>
+      <c r="CY97" s="23"/>
       <c r="CZ97" s="31"/>
       <c r="DA97" s="31"/>
       <c r="DB97" s="31"/>
+      <c r="DC97" s="31"/>
     </row>
     <row r="98" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A98" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="CY98" s="25"/>
       <c r="CZ98" s="25"/>
       <c r="DA98" s="25"/>
       <c r="DB98" s="25"/>
+      <c r="DC98" s="25"/>
     </row>
     <row r="99" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B99" s="7"/>
@@ -19558,12 +19653,12 @@
       <c r="CU99" s="21"/>
       <c r="CV99" s="21"/>
       <c r="CW99" s="21"/>
-      <c r="CX99" s="30"/>
-      <c r="CY99" s="30"/>
+      <c r="CX99" s="21"/>
+      <c r="CY99" s="21"/>
       <c r="CZ99" s="30"/>
       <c r="DA99" s="30"/>
       <c r="DB99" s="30"/>
-      <c r="DC99" s="7"/>
+      <c r="DC99" s="30"/>
       <c r="DD99" s="7"/>
       <c r="DE99" s="7"/>
       <c r="DF99" s="7"/>
@@ -19739,7 +19834,7 @@
       <c r="CZ100" s="21"/>
       <c r="DA100" s="21"/>
       <c r="DB100" s="21"/>
-      <c r="DC100" s="7"/>
+      <c r="DC100" s="21"/>
       <c r="DD100" s="7"/>
       <c r="DE100" s="7"/>
       <c r="DF100" s="7"/>
@@ -19816,7 +19911,7 @@
     </row>
     <row r="102" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104" spans="1:179" x14ac:dyDescent="0.2">
@@ -19826,7 +19921,7 @@
     </row>
     <row r="105" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:179" x14ac:dyDescent="0.2">
@@ -19995,6 +20090,7 @@
       <c r="DB108" s="19">
         <v>2026</v>
       </c>
+      <c r="DC108" s="19"/>
     </row>
     <row r="109" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
@@ -20312,6 +20408,9 @@
       </c>
       <c r="DB109" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC109" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -20634,9 +20733,11 @@
         <v>112.67482589868681</v>
       </c>
       <c r="DB111" s="28">
-        <v>110.61787358554889</v>
-      </c>
-      <c r="DC111" s="7"/>
+        <v>110.60914573630589</v>
+      </c>
+      <c r="DC111" s="28">
+        <v>124.74396064009443</v>
+      </c>
       <c r="DD111" s="7"/>
       <c r="DE111" s="7"/>
       <c r="DF111" s="7"/>
@@ -21027,9 +21128,11 @@
         <v>119.81180296023084</v>
       </c>
       <c r="DB112" s="28">
-        <v>89.847840851201255</v>
-      </c>
-      <c r="DC112" s="7"/>
+        <v>89.847840851201241</v>
+      </c>
+      <c r="DC112" s="28">
+        <v>134.90700370683774</v>
+      </c>
       <c r="DD112" s="7"/>
       <c r="DE112" s="7"/>
       <c r="DF112" s="7"/>
@@ -21422,7 +21525,9 @@
       <c r="DB113" s="28">
         <v>130.55164428200879</v>
       </c>
-      <c r="DC113" s="7"/>
+      <c r="DC113" s="28">
+        <v>134.32022259835981</v>
+      </c>
       <c r="DD113" s="7"/>
       <c r="DE113" s="7"/>
       <c r="DF113" s="7"/>
@@ -21815,7 +21920,9 @@
       <c r="DB114" s="28">
         <v>101.00868726806563</v>
       </c>
-      <c r="DC114" s="7"/>
+      <c r="DC114" s="28">
+        <v>125.67604792001381</v>
+      </c>
       <c r="DD114" s="7"/>
       <c r="DE114" s="7"/>
       <c r="DF114" s="7"/>
@@ -22208,7 +22315,9 @@
       <c r="DB115" s="28">
         <v>96.963140221228102</v>
       </c>
-      <c r="DC115" s="7"/>
+      <c r="DC115" s="28">
+        <v>130.19850783238704</v>
+      </c>
       <c r="DD115" s="7"/>
       <c r="DE115" s="7"/>
       <c r="DF115" s="7"/>
@@ -22599,9 +22708,11 @@
         <v>120.52499186465822</v>
       </c>
       <c r="DB116" s="28">
-        <v>95.100186615150434</v>
-      </c>
-      <c r="DC116" s="7"/>
+        <v>95.100186615150449</v>
+      </c>
+      <c r="DC116" s="28">
+        <v>128.2161740388006</v>
+      </c>
       <c r="DD116" s="7"/>
       <c r="DE116" s="7"/>
       <c r="DF116" s="7"/>
@@ -22994,7 +23105,9 @@
       <c r="DB117" s="28">
         <v>96.402578089174796</v>
       </c>
-      <c r="DC117" s="7"/>
+      <c r="DC117" s="28">
+        <v>130.54037325219545</v>
+      </c>
       <c r="DD117" s="7"/>
       <c r="DE117" s="7"/>
       <c r="DF117" s="7"/>
@@ -23387,7 +23500,9 @@
       <c r="DB118" s="28">
         <v>96.74594462234964</v>
       </c>
-      <c r="DC118" s="7"/>
+      <c r="DC118" s="28">
+        <v>132.13045483132211</v>
+      </c>
       <c r="DD118" s="7"/>
       <c r="DE118" s="7"/>
       <c r="DF118" s="7"/>
@@ -23567,7 +23682,7 @@
       <c r="CZ119" s="21"/>
       <c r="DA119" s="21"/>
       <c r="DB119" s="21"/>
-      <c r="DC119" s="7"/>
+      <c r="DC119" s="21"/>
       <c r="DD119" s="7"/>
       <c r="DE119" s="7"/>
       <c r="DF119" s="7"/>
@@ -23958,9 +24073,11 @@
         <v>112.25393438742854</v>
       </c>
       <c r="DB120" s="28">
-        <v>112.11664185276864</v>
-      </c>
-      <c r="DC120" s="7"/>
+        <v>111.95995442528964</v>
+      </c>
+      <c r="DC120" s="28">
+        <v>130.61594685485485</v>
+      </c>
       <c r="DD120" s="7"/>
       <c r="DE120" s="7"/>
       <c r="DF120" s="7"/>
@@ -24141,6 +24258,7 @@
       <c r="CZ121" s="23"/>
       <c r="DA121" s="23"/>
       <c r="DB121" s="23"/>
+      <c r="DC121" s="23"/>
     </row>
     <row r="122" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A122" s="9" t="s">
@@ -24159,7 +24277,7 @@
     </row>
     <row r="127" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129" spans="1:179" x14ac:dyDescent="0.2">
@@ -24169,7 +24287,7 @@
     </row>
     <row r="130" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="1:179" x14ac:dyDescent="0.2">
@@ -24338,6 +24456,7 @@
       <c r="DB133" s="19">
         <v>2026</v>
       </c>
+      <c r="DC133" s="19"/>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
@@ -24655,6 +24774,9 @@
       </c>
       <c r="DB134" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC134" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -24977,9 +25099,11 @@
         <v>14.900584508539961</v>
       </c>
       <c r="DB136" s="17">
-        <v>14.795526176149531</v>
-      </c>
-      <c r="DC136" s="7"/>
+        <v>14.260926887711761</v>
+      </c>
+      <c r="DC136" s="17">
+        <v>20.11522141886439</v>
+      </c>
       <c r="DD136" s="7"/>
       <c r="DE136" s="7"/>
       <c r="DF136" s="7"/>
@@ -25370,9 +25494,11 @@
         <v>2.3074966152800478</v>
       </c>
       <c r="DB137" s="17">
-        <v>4.3924988098370816</v>
-      </c>
-      <c r="DC137" s="7"/>
+        <v>4.3777173297000038</v>
+      </c>
+      <c r="DC137" s="17">
+        <v>7.1682067067617261</v>
+      </c>
       <c r="DD137" s="7"/>
       <c r="DE137" s="7"/>
       <c r="DF137" s="7"/>
@@ -25763,9 +25889,11 @@
         <v>57.185115343698754</v>
       </c>
       <c r="DB138" s="17">
-        <v>48.122306060117367</v>
-      </c>
-      <c r="DC138" s="7"/>
+        <v>47.959915663509165</v>
+      </c>
+      <c r="DC138" s="17">
+        <v>37.063269867531488</v>
+      </c>
       <c r="DD138" s="7"/>
       <c r="DE138" s="7"/>
       <c r="DF138" s="7"/>
@@ -26156,9 +26284,11 @@
         <v>0.96531168716189519</v>
       </c>
       <c r="DB139" s="17">
-        <v>0.95755837650342968</v>
-      </c>
-      <c r="DC139" s="7"/>
+        <v>0.96778510956775243</v>
+      </c>
+      <c r="DC139" s="17">
+        <v>0.99414436464173916</v>
+      </c>
       <c r="DD139" s="7"/>
       <c r="DE139" s="7"/>
       <c r="DF139" s="7"/>
@@ -26549,9 +26679,11 @@
         <v>3.5658341166517831</v>
       </c>
       <c r="DB140" s="17">
-        <v>5.5472565495368711</v>
-      </c>
-      <c r="DC140" s="7"/>
+        <v>5.3912230214211734</v>
+      </c>
+      <c r="DC140" s="17">
+        <v>5.8356617114596121</v>
+      </c>
       <c r="DD140" s="7"/>
       <c r="DE140" s="7"/>
       <c r="DF140" s="7"/>
@@ -26942,9 +27074,11 @@
         <v>14.012072400911691</v>
       </c>
       <c r="DB141" s="17">
-        <v>18.425910637727767</v>
-      </c>
-      <c r="DC141" s="7"/>
+        <v>19.071386575663869</v>
+      </c>
+      <c r="DC141" s="17">
+        <v>18.564028132022116</v>
+      </c>
       <c r="DD141" s="7"/>
       <c r="DE141" s="7"/>
       <c r="DF141" s="7"/>
@@ -27335,9 +27469,11 @@
         <v>0.81900559499963554</v>
       </c>
       <c r="DB142" s="17">
-        <v>1.0170321882363593</v>
-      </c>
-      <c r="DC142" s="7"/>
+        <v>1.2232267710207247</v>
+      </c>
+      <c r="DC142" s="17">
+        <v>1.2968585156097299</v>
+      </c>
       <c r="DD142" s="7"/>
       <c r="DE142" s="7"/>
       <c r="DF142" s="7"/>
@@ -27728,9 +27864,11 @@
         <v>6.2445797327562484</v>
       </c>
       <c r="DB143" s="17">
-        <v>6.7419112018915932</v>
-      </c>
-      <c r="DC143" s="7"/>
+        <v>6.747818641405563</v>
+      </c>
+      <c r="DC143" s="17">
+        <v>8.9626092831092112</v>
+      </c>
       <c r="DD143" s="7"/>
       <c r="DE143" s="7"/>
       <c r="DF143" s="7"/>
@@ -27910,7 +28048,7 @@
       <c r="CZ144" s="21"/>
       <c r="DA144" s="21"/>
       <c r="DB144" s="21"/>
-      <c r="DC144" s="7"/>
+      <c r="DC144" s="21"/>
       <c r="DD144" s="7"/>
       <c r="DE144" s="7"/>
       <c r="DF144" s="7"/>
@@ -28303,7 +28441,9 @@
       <c r="DB145" s="28">
         <v>100</v>
       </c>
-      <c r="DC145" s="7"/>
+      <c r="DC145" s="28">
+        <v>100</v>
+      </c>
       <c r="DD145" s="7"/>
       <c r="DE145" s="7"/>
       <c r="DF145" s="7"/>
@@ -28484,6 +28624,7 @@
       <c r="CZ146" s="23"/>
       <c r="DA146" s="23"/>
       <c r="DB146" s="23"/>
+      <c r="DC146" s="23"/>
     </row>
     <row r="147" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A147" s="9" t="s">
@@ -28596,7 +28737,7 @@
       <c r="CZ148" s="21"/>
       <c r="DA148" s="21"/>
       <c r="DB148" s="21"/>
-      <c r="DC148" s="7"/>
+      <c r="DC148" s="21"/>
       <c r="DD148" s="7"/>
       <c r="DE148" s="7"/>
       <c r="DF148" s="7"/>
@@ -28776,7 +28917,7 @@
       <c r="CZ149" s="21"/>
       <c r="DA149" s="21"/>
       <c r="DB149" s="21"/>
-      <c r="DC149" s="7"/>
+      <c r="DC149" s="21"/>
       <c r="DD149" s="7"/>
       <c r="DE149" s="7"/>
       <c r="DF149" s="7"/>
@@ -28862,7 +29003,7 @@
     </row>
     <row r="152" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="154" spans="1:179" x14ac:dyDescent="0.2">
@@ -28872,7 +29013,7 @@
     </row>
     <row r="155" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="156" spans="1:179" x14ac:dyDescent="0.2">
@@ -29041,6 +29182,7 @@
       <c r="DB158" s="19">
         <v>2026</v>
       </c>
+      <c r="DC158" s="19"/>
     </row>
     <row r="159" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
@@ -29358,6 +29500,9 @@
       </c>
       <c r="DB159" s="15" t="s">
         <v>2</v>
+      </c>
+      <c r="DC159" s="15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:179" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -29680,9 +29825,11 @@
         <v>14.844924076119412</v>
       </c>
       <c r="DB161" s="17">
-        <v>14.995991656192253</v>
-      </c>
-      <c r="DC161" s="7"/>
+        <v>14.435087747780315</v>
+      </c>
+      <c r="DC161" s="17">
+        <v>21.062091329618699</v>
+      </c>
       <c r="DD161" s="7"/>
       <c r="DE161" s="7"/>
       <c r="DF161" s="7"/>
@@ -30073,9 +30220,11 @@
         <v>2.1619370316698956</v>
       </c>
       <c r="DB162" s="17">
-        <v>5.4811803070127123</v>
-      </c>
-      <c r="DC162" s="7"/>
+        <v>5.4551008469054389</v>
+      </c>
+      <c r="DC162" s="17">
+        <v>6.9402038480493546</v>
+      </c>
       <c r="DD162" s="7"/>
       <c r="DE162" s="7"/>
       <c r="DF162" s="7"/>
@@ -30466,9 +30615,11 @@
         <v>59.317852819985561</v>
       </c>
       <c r="DB163" s="17">
-        <v>41.32702719558943</v>
-      </c>
-      <c r="DC163" s="7"/>
+        <v>41.1300064542136</v>
+      </c>
+      <c r="DC163" s="17">
+        <v>36.04114104069204</v>
+      </c>
       <c r="DD163" s="7"/>
       <c r="DE163" s="7"/>
       <c r="DF163" s="7"/>
@@ -30859,9 +31010,11 @@
         <v>0.92237383337710321</v>
       </c>
       <c r="DB164" s="17">
-        <v>1.0628613484168645</v>
-      </c>
-      <c r="DC164" s="7"/>
+        <v>1.0727114636498782</v>
+      </c>
+      <c r="DC164" s="17">
+        <v>1.0332208057715362</v>
+      </c>
       <c r="DD164" s="7"/>
       <c r="DE164" s="7"/>
       <c r="DF164" s="7"/>
@@ -31252,9 +31405,11 @@
         <v>3.2851533217038336</v>
       </c>
       <c r="DB165" s="17">
-        <v>6.4141876429625935</v>
-      </c>
-      <c r="DC165" s="7"/>
+        <v>6.2250570928058773</v>
+      </c>
+      <c r="DC165" s="17">
+        <v>5.8543718561520581</v>
+      </c>
       <c r="DD165" s="7"/>
       <c r="DE165" s="7"/>
       <c r="DF165" s="7"/>
@@ -31645,9 +31800,11 @@
         <v>13.050490455042851</v>
       </c>
       <c r="DB166" s="17">
-        <v>21.722893480128384</v>
-      </c>
-      <c r="DC166" s="7"/>
+        <v>22.452443552810468</v>
+      </c>
+      <c r="DC166" s="17">
+        <v>18.911483906628302</v>
+      </c>
       <c r="DD166" s="7"/>
       <c r="DE166" s="7"/>
       <c r="DF166" s="7"/>
@@ -32038,9 +32195,11 @@
         <v>0.75509059194150552</v>
       </c>
       <c r="DB167" s="17">
-        <v>1.1828131141446898</v>
-      </c>
-      <c r="DC167" s="7"/>
+        <v>1.4206301973437903</v>
+      </c>
+      <c r="DC167" s="17">
+        <v>1.2976093045627752</v>
+      </c>
       <c r="DD167" s="7"/>
       <c r="DE167" s="7"/>
       <c r="DF167" s="7"/>
@@ -32431,9 +32590,11 @@
         <v>5.6621778701598204</v>
       </c>
       <c r="DB168" s="17">
-        <v>7.8130452555530683</v>
-      </c>
-      <c r="DC168" s="7"/>
+        <v>7.8089626444906219</v>
+      </c>
+      <c r="DC168" s="17">
+        <v>8.859877908525231</v>
+      </c>
       <c r="DD168" s="7"/>
       <c r="DE168" s="7"/>
       <c r="DF168" s="7"/>
@@ -32613,7 +32774,7 @@
       <c r="CZ169" s="21"/>
       <c r="DA169" s="21"/>
       <c r="DB169" s="21"/>
-      <c r="DC169" s="7"/>
+      <c r="DC169" s="21"/>
       <c r="DD169" s="7"/>
       <c r="DE169" s="7"/>
       <c r="DF169" s="7"/>
@@ -33006,7 +33167,9 @@
       <c r="DB170" s="28">
         <v>100</v>
       </c>
-      <c r="DC170" s="7"/>
+      <c r="DC170" s="28">
+        <v>100</v>
+      </c>
       <c r="DD170" s="7"/>
       <c r="DE170" s="7"/>
       <c r="DF170" s="7"/>
@@ -33187,6 +33350,7 @@
       <c r="CZ171" s="23"/>
       <c r="DA171" s="23"/>
       <c r="DB171" s="23"/>
+      <c r="DC171" s="23"/>
     </row>
     <row r="172" spans="1:179" x14ac:dyDescent="0.2">
       <c r="A172" s="9" t="s">
@@ -33300,7 +33464,7 @@
       <c r="CZ173" s="32"/>
       <c r="DA173" s="32"/>
       <c r="DB173" s="32"/>
-      <c r="DC173" s="12"/>
+      <c r="DC173" s="32"/>
       <c r="DD173" s="12"/>
       <c r="DE173" s="12"/>
       <c r="DF173" s="12"/>
@@ -33379,9 +33543,9 @@
   <pageSetup paperSize="9" scale="50" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="50" max="105" man="1"/>
-    <brk id="100" max="105" man="1"/>
-    <brk id="124" max="105" man="1"/>
+    <brk id="50" max="106" man="1"/>
+    <brk id="100" max="106" man="1"/>
+    <brk id="124" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>